--- a/grupos/3BLCM - Estadisticos 20221.xlsx
+++ b/grupos/3BLCM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="188">
   <si>
     <t>Materia</t>
   </si>
@@ -119,7 +119,7 @@
     <t>MARTINEZ ZARATE DIANA CRISTINA</t>
   </si>
   <si>
-    <t>MOLOHUA SÁNCHEZ OLIVA</t>
+    <t>MOLOHUA SANCHEZ OLIVA</t>
   </si>
   <si>
     <t>MONTALVO PANZO ADAL</t>
@@ -224,15 +224,15 @@
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
+    <t>Caballero Rosas María Teresa</t>
+  </si>
+  <si>
     <t>Ángel Martínez Noe Cristobal</t>
   </si>
   <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
-    <t>Caballero Rosas María Teresa</t>
-  </si>
-  <si>
     <t>Flores González Ángel</t>
   </si>
   <si>
@@ -248,328 +248,325 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>VILLASEÑOR</t>
+  </si>
+  <si>
+    <t>MONICA AIME</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>BALDERAS</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
     <t>CHICO</t>
   </si>
   <si>
-    <t>OFICIAL</t>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>DOLORES</t>
+  </si>
+  <si>
+    <t>FRANCO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>JUSTO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>MOTA</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>PALAFOX</t>
+  </si>
+  <si>
+    <t>PASTRANA</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
   </si>
   <si>
     <t>ROJAS</t>
   </si>
   <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>GAMBINO</t>
+  </si>
+  <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>GIL</t>
   </si>
   <si>
-    <t>VILLASEÑOR</t>
+    <t>TINOCO</t>
+  </si>
+  <si>
+    <t>MATA</t>
+  </si>
+  <si>
+    <t>TIBURCIO</t>
+  </si>
+  <si>
+    <t>MONTERO</t>
+  </si>
+  <si>
+    <t>NEGRETE</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>MONGE</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>FLOURENS</t>
+  </si>
+  <si>
+    <t>LIMON</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
   </si>
   <si>
     <t>VENEGAS</t>
   </si>
   <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>ESPINDOLA</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>RUTH</t>
+  </si>
+  <si>
+    <t>AXEL EDUARDO</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>CARLOS EMILIO</t>
+  </si>
+  <si>
+    <t>PERLA</t>
+  </si>
+  <si>
     <t>ATZIRI</t>
   </si>
   <si>
-    <t>MONICA AIME</t>
+    <t>EDNA</t>
+  </si>
+  <si>
+    <t>AMISADAI</t>
+  </si>
+  <si>
+    <t>ZURISADAI</t>
+  </si>
+  <si>
+    <t>CRISTOPHER</t>
+  </si>
+  <si>
+    <t>AMY JULIET</t>
+  </si>
+  <si>
+    <t>LUIS CARLOS</t>
+  </si>
+  <si>
+    <t>YAMILET MONSERRAT</t>
+  </si>
+  <si>
+    <t>YULIET</t>
+  </si>
+  <si>
+    <t>DARLA MARLENE</t>
+  </si>
+  <si>
+    <t>MARIA MICHELLE</t>
+  </si>
+  <si>
+    <t>ANETTE JOCELYN</t>
+  </si>
+  <si>
+    <t>JOSE RAFAEL</t>
+  </si>
+  <si>
+    <t>DIANA CRISTINA</t>
+  </si>
+  <si>
+    <t>NAHOMY</t>
+  </si>
+  <si>
+    <t>ANGEL DIEGO</t>
+  </si>
+  <si>
+    <t>ADAL</t>
+  </si>
+  <si>
+    <t>OLIVA</t>
+  </si>
+  <si>
+    <t>SAIRA LEILANI</t>
+  </si>
+  <si>
+    <t>ARACELY</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
+    <t>MARIAM</t>
+  </si>
+  <si>
+    <t>GONZALO</t>
+  </si>
+  <si>
+    <t>ROSA JAZMIN</t>
+  </si>
+  <si>
+    <t>REBECA</t>
+  </si>
+  <si>
+    <t>BRIGITTE</t>
+  </si>
+  <si>
+    <t>SAYURI BETSABE</t>
+  </si>
+  <si>
+    <t>ANA KAREN</t>
+  </si>
+  <si>
+    <t>ANA LAURA</t>
+  </si>
+  <si>
+    <t>DIEGO EMILIO</t>
   </si>
   <si>
     <t>ANDRIK YOSIMAR</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>DOLORES</t>
-  </si>
-  <si>
-    <t>FRANCO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>JUSTO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>MOTA</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>PALAFOX</t>
-  </si>
-  <si>
-    <t>PASTRANA</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>GAMBINO</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>MATA</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>MONTERO</t>
-  </si>
-  <si>
-    <t>NEGRETE</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>SÁNCHEZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>MONGE</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>FLOURENS</t>
-  </si>
-  <si>
-    <t>LIMON</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>ESPINDOLA</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>RUTH</t>
-  </si>
-  <si>
-    <t>AXEL EDUARDO</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>CARLOS EMILIO</t>
-  </si>
-  <si>
-    <t>PERLA</t>
-  </si>
-  <si>
-    <t>EDNA</t>
-  </si>
-  <si>
-    <t>AMISADAI</t>
-  </si>
-  <si>
-    <t>ZURISADAI</t>
-  </si>
-  <si>
-    <t>CRISTOPHER</t>
-  </si>
-  <si>
-    <t>AMY JULIET</t>
-  </si>
-  <si>
-    <t>LUIS CARLOS</t>
-  </si>
-  <si>
-    <t>YAMILET MONSERRAT</t>
-  </si>
-  <si>
-    <t>YULIET</t>
-  </si>
-  <si>
-    <t>DARLA MARLENE</t>
-  </si>
-  <si>
-    <t>MARIA MICHELLE</t>
-  </si>
-  <si>
-    <t>ANETTE JOCELYN</t>
-  </si>
-  <si>
-    <t>JOSE RAFAEL</t>
-  </si>
-  <si>
-    <t>DIANA CRISTINA</t>
-  </si>
-  <si>
-    <t>NAHOMY</t>
-  </si>
-  <si>
-    <t>ANGEL DIEGO</t>
-  </si>
-  <si>
-    <t>ADAL</t>
-  </si>
-  <si>
-    <t>OLIVA</t>
-  </si>
-  <si>
-    <t>SAIRA LEILANI</t>
-  </si>
-  <si>
-    <t>ARACELY</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>MARIAM</t>
-  </si>
-  <si>
-    <t>GONZALO</t>
-  </si>
-  <si>
-    <t>ROSA JAZMIN</t>
-  </si>
-  <si>
-    <t>REBECA</t>
-  </si>
-  <si>
-    <t>BRIGITTE</t>
-  </si>
-  <si>
-    <t>SAYURI BETSABE</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
-  </si>
-  <si>
-    <t>ANA LAURA</t>
-  </si>
-  <si>
-    <t>DIEGO EMILIO</t>
   </si>
   <si>
     <t>IVANNA DANIELA</t>
@@ -1094,13 +1091,13 @@
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -1130,13 +1127,13 @@
         <v>8</v>
       </c>
       <c r="V4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W4">
         <v>7</v>
       </c>
       <c r="X4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y4">
         <v>7</v>
@@ -1171,13 +1168,13 @@
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -1213,7 +1210,7 @@
         <v>8</v>
       </c>
       <c r="X5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y5">
         <v>6</v>
@@ -1248,13 +1245,13 @@
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -1284,10 +1281,10 @@
         <v>8</v>
       </c>
       <c r="V6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X6">
         <v>9</v>
@@ -1325,13 +1322,13 @@
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -1402,13 +1399,13 @@
         <v>-1</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1438,13 +1435,13 @@
         <v>7</v>
       </c>
       <c r="V8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>6</v>
@@ -1479,13 +1476,13 @@
         <v>-1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1515,13 +1512,13 @@
         <v>9</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y9">
         <v>7</v>
@@ -1532,7 +1529,7 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C10">
         <v>5</v>
@@ -1547,7 +1544,7 @@
         <v>5</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H10">
         <v>-1</v>
@@ -1556,13 +1553,13 @@
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1586,7 +1583,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U10">
         <v>5</v>
@@ -1601,7 +1598,7 @@
         <v>5</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1633,13 +1630,13 @@
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -1669,10 +1666,10 @@
         <v>8</v>
       </c>
       <c r="V11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X11">
         <v>9</v>
@@ -1710,13 +1707,13 @@
         <v>-1</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -1749,10 +1746,10 @@
         <v>8</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y12">
         <v>5</v>
@@ -1787,13 +1784,13 @@
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -1829,7 +1826,7 @@
         <v>8</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y13">
         <v>5</v>
@@ -1864,13 +1861,13 @@
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1903,10 +1900,10 @@
         <v>9</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y14">
         <v>7</v>
@@ -1941,13 +1938,13 @@
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -1983,7 +1980,7 @@
         <v>8</v>
       </c>
       <c r="X15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y15">
         <v>6</v>
@@ -2018,13 +2015,13 @@
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -2060,7 +2057,7 @@
         <v>7</v>
       </c>
       <c r="X16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y16">
         <v>5</v>
@@ -2095,13 +2092,13 @@
         <v>-1</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -2131,10 +2128,10 @@
         <v>8</v>
       </c>
       <c r="V17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X17">
         <v>6</v>
@@ -2172,13 +2169,13 @@
         <v>-1</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -2214,7 +2211,7 @@
         <v>6</v>
       </c>
       <c r="X18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y18">
         <v>7</v>
@@ -2249,13 +2246,13 @@
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -2285,13 +2282,13 @@
         <v>6</v>
       </c>
       <c r="V19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W19">
         <v>8</v>
       </c>
       <c r="X19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>5</v>
@@ -2326,13 +2323,13 @@
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -2403,13 +2400,13 @@
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2439,13 +2436,13 @@
         <v>7</v>
       </c>
       <c r="V21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W21">
         <v>5</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y21">
         <v>6</v>
@@ -2480,13 +2477,13 @@
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -2516,13 +2513,13 @@
         <v>6</v>
       </c>
       <c r="V22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y22">
         <v>6</v>
@@ -2557,13 +2554,13 @@
         <v>-1</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M23">
         <v>-1</v>
@@ -2596,7 +2593,7 @@
         <v>8</v>
       </c>
       <c r="W23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X23">
         <v>7</v>
@@ -2634,13 +2631,13 @@
         <v>-1</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -2673,10 +2670,10 @@
         <v>8</v>
       </c>
       <c r="W24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X24">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y24">
         <v>8</v>
@@ -2711,13 +2708,13 @@
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -2788,13 +2785,13 @@
         <v>-1</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -2827,10 +2824,10 @@
         <v>8</v>
       </c>
       <c r="W26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y26">
         <v>8</v>
@@ -2900,7 +2897,7 @@
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M28">
         <v>-1</v>
@@ -2974,10 +2971,10 @@
         <v>-1</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M29">
         <v>-1</v>
@@ -3013,7 +3010,7 @@
         <v>5</v>
       </c>
       <c r="X29">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y29">
         <v>5</v>
@@ -3048,13 +3045,13 @@
         <v>-1</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M30">
         <v>-1</v>
@@ -3087,7 +3084,7 @@
         <v>5</v>
       </c>
       <c r="W30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X30">
         <v>5</v>
@@ -3125,13 +3122,13 @@
         <v>-1</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M31">
         <v>-1</v>
@@ -3167,7 +3164,7 @@
         <v>8</v>
       </c>
       <c r="X31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y31">
         <v>7</v>
@@ -3202,13 +3199,13 @@
         <v>-1</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -3238,13 +3235,13 @@
         <v>6</v>
       </c>
       <c r="V32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W32">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y32">
         <v>7</v>
@@ -3279,13 +3276,13 @@
         <v>-1</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M33">
         <v>-1</v>
@@ -3318,10 +3315,10 @@
         <v>6</v>
       </c>
       <c r="W33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y33">
         <v>7</v>
@@ -3356,13 +3353,13 @@
         <v>-1</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K34">
         <v>-1</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M34">
         <v>-1</v>
@@ -3398,7 +3395,7 @@
         <v>7</v>
       </c>
       <c r="X34">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y34">
         <v>7</v>
@@ -3433,13 +3430,13 @@
         <v>-1</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M35">
         <v>-1</v>
@@ -3472,7 +3469,7 @@
         <v>8</v>
       </c>
       <c r="W35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X35">
         <v>10</v>
@@ -3510,13 +3507,13 @@
         <v>-1</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M36">
         <v>-1</v>
@@ -3549,7 +3546,7 @@
         <v>7</v>
       </c>
       <c r="W36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X36">
         <v>5</v>
@@ -3587,13 +3584,13 @@
         <v>-1</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M37">
         <v>-1</v>
@@ -3626,7 +3623,7 @@
         <v>8</v>
       </c>
       <c r="W37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X37">
         <v>10</v>
@@ -3664,13 +3661,13 @@
         <v>-1</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M38">
         <v>-1</v>
@@ -3700,7 +3697,7 @@
         <v>8</v>
       </c>
       <c r="V38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W38">
         <v>8</v>
@@ -3741,13 +3738,13 @@
         <v>-1</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M39">
         <v>-1</v>
@@ -3777,7 +3774,7 @@
         <v>7</v>
       </c>
       <c r="V39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W39">
         <v>7</v>
@@ -3818,13 +3815,13 @@
         <v>-1</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M40">
         <v>-1</v>
@@ -3854,7 +3851,7 @@
         <v>8</v>
       </c>
       <c r="V40">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W40">
         <v>8</v>
@@ -3895,13 +3892,13 @@
         <v>-1</v>
       </c>
       <c r="J41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M41">
         <v>-1</v>
@@ -3937,7 +3934,7 @@
         <v>8</v>
       </c>
       <c r="X41">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y41">
         <v>5</v>
@@ -3948,7 +3945,7 @@
         <v>50</v>
       </c>
       <c r="B42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C42">
         <v>5</v>
@@ -3972,13 +3969,13 @@
         <v>-1</v>
       </c>
       <c r="J42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M42">
         <v>-1</v>
@@ -4002,7 +3999,7 @@
         <v>-1</v>
       </c>
       <c r="T42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U42">
         <v>5</v>
@@ -4049,13 +4046,13 @@
         <v>-1</v>
       </c>
       <c r="J43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M43">
         <v>-1</v>
@@ -4085,7 +4082,7 @@
         <v>6</v>
       </c>
       <c r="V43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W43">
         <v>5</v>
@@ -4126,13 +4123,13 @@
         <v>-1</v>
       </c>
       <c r="J44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M44">
         <v>-1</v>
@@ -4165,7 +4162,7 @@
         <v>9</v>
       </c>
       <c r="W44">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X44">
         <v>7</v>
@@ -4203,13 +4200,13 @@
         <v>-1</v>
       </c>
       <c r="J45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M45">
         <v>-1</v>
@@ -4280,13 +4277,13 @@
         <v>-1</v>
       </c>
       <c r="J46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M46">
         <v>-1</v>
@@ -4316,7 +4313,7 @@
         <v>6</v>
       </c>
       <c r="V46">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W46">
         <v>6</v>
@@ -4357,13 +4354,13 @@
         <v>-1</v>
       </c>
       <c r="J47">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K47">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L47">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M47">
         <v>-1</v>
@@ -4393,10 +4390,10 @@
         <v>9</v>
       </c>
       <c r="V47">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W47">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X47">
         <v>9</v>
@@ -4434,13 +4431,13 @@
         <v>-1</v>
       </c>
       <c r="J48">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K48">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L48">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M48">
         <v>-1</v>
@@ -4470,10 +4467,10 @@
         <v>7</v>
       </c>
       <c r="V48">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W48">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X48">
         <v>5</v>
@@ -4547,22 +4544,22 @@
         <v>31</v>
       </c>
       <c r="E2">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2">
         <v>70.45</v>
       </c>
       <c r="G2">
-        <v>27.27</v>
+        <v>29.55</v>
       </c>
       <c r="H2">
         <v>6.3</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>2.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -4576,19 +4573,19 @@
         <v>44</v>
       </c>
       <c r="D3">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>81.81999999999999</v>
+        <v>88.64</v>
       </c>
       <c r="G3">
-        <v>18.18</v>
+        <v>11.36</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4599,7 +4596,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
@@ -4608,51 +4605,51 @@
         <v>45</v>
       </c>
       <c r="D4">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>86.67</v>
+        <v>88.89</v>
       </c>
       <c r="G4">
-        <v>13.33</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>69</v>
       </c>
       <c r="C5">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D5">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>93.18000000000001</v>
+        <v>88.89</v>
       </c>
       <c r="G5">
-        <v>6.82</v>
+        <v>11.11</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4663,34 +4660,34 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>70</v>
       </c>
       <c r="C6">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D6">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>93.33</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="G6">
-        <v>4.44</v>
+        <v>6.82</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>2.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -4707,22 +4704,22 @@
         <v>42</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7">
         <v>95.45</v>
       </c>
       <c r="G7">
+        <v>4.55</v>
+      </c>
+      <c r="H7">
+        <v>8.9</v>
+      </c>
+      <c r="I7">
         <v>0</v>
       </c>
-      <c r="H7">
-        <v>9.1</v>
-      </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
       <c r="J7">
-        <v>4.55</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4732,7 +4729,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4761,82 +4758,22 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2">
-        <v>21330051920296</v>
+        <v>21330051920311</v>
       </c>
       <c r="B2" t="s">
         <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920296</v>
-      </c>
-      <c r="B3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920311</v>
-      </c>
-      <c r="B4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C4" t="s">
-        <v>80</v>
-      </c>
-      <c r="D4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920324</v>
-      </c>
-      <c r="B5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C5" t="s">
-        <v>81</v>
-      </c>
-      <c r="D5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -4872,67 +4809,67 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920296</v>
+        <v>21330051920311</v>
       </c>
       <c r="B2" t="s">
         <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920311</v>
+        <v>21330051920289</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>145</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920324</v>
+        <v>21330051920290</v>
       </c>
       <c r="B4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920289</v>
+        <v>21330051920291</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -4940,16 +4877,16 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920290</v>
+        <v>21330051920292</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -4957,16 +4894,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920291</v>
+        <v>21330051920293</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C7" t="s">
-        <v>123</v>
+        <v>92</v>
       </c>
       <c r="D7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -4974,16 +4911,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920292</v>
+        <v>21330051920294</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C8" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -4991,16 +4928,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920293</v>
+        <v>21330051920295</v>
       </c>
       <c r="B9" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C9" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="D9" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -5008,16 +4945,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920294</v>
+        <v>21330051920296</v>
       </c>
       <c r="B10" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -5025,16 +4962,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920295</v>
+        <v>21330051920297</v>
       </c>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>126</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -5042,16 +4979,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920297</v>
+        <v>21330051920298</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="D12" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -5059,16 +4996,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920298</v>
+        <v>21330051920299</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C13" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -5076,16 +5013,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920299</v>
+        <v>21330051920337</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C14" t="s">
-        <v>122</v>
+        <v>83</v>
       </c>
       <c r="D14" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -5093,16 +5030,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920337</v>
+        <v>21330051920300</v>
       </c>
       <c r="B15" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="D15" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -5110,16 +5047,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920300</v>
+        <v>21330051920301</v>
       </c>
       <c r="B16" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D16" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -5127,16 +5064,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920301</v>
+        <v>21330051920302</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C17" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -5144,16 +5081,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920302</v>
+        <v>21330051920303</v>
       </c>
       <c r="B18" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C18" t="s">
-        <v>129</v>
+        <v>91</v>
       </c>
       <c r="D18" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -5161,16 +5098,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920303</v>
+        <v>21330051920304</v>
       </c>
       <c r="B19" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="D19" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -5178,16 +5115,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920304</v>
+        <v>21330051920305</v>
       </c>
       <c r="B20" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C20" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D20" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -5195,16 +5132,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920305</v>
+        <v>21330051920306</v>
       </c>
       <c r="B21" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C21" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="D21" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -5212,16 +5149,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>21330051920306</v>
+        <v>20330051920235</v>
       </c>
       <c r="B22" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C22" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="D22" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -5229,16 +5166,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920235</v>
+        <v>21330051920307</v>
       </c>
       <c r="B23" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C23" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D23" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -5246,16 +5183,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>21330051920307</v>
+        <v>19330051920208</v>
       </c>
       <c r="B24" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C24" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D24" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -5263,16 +5200,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>19330051920208</v>
+        <v>21330051920308</v>
       </c>
       <c r="B25" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C25" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D25" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -5280,16 +5217,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920308</v>
+        <v>21330051920309</v>
       </c>
       <c r="B26" t="s">
+        <v>99</v>
+      </c>
+      <c r="C26" t="s">
         <v>103</v>
       </c>
-      <c r="C26" t="s">
-        <v>135</v>
-      </c>
       <c r="D26" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -5297,16 +5234,16 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920309</v>
+        <v>21330051920090</v>
       </c>
       <c r="B27" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C27" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="D27" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -5314,16 +5251,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920090</v>
+        <v>21330051920310</v>
       </c>
       <c r="B28" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C28" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D28" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -5331,16 +5268,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>21330051920310</v>
+        <v>21330051920312</v>
       </c>
       <c r="B29" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C29" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D29" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -5348,16 +5285,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>21330051920312</v>
+        <v>21330051920313</v>
       </c>
       <c r="B30" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C30" t="s">
-        <v>132</v>
+        <v>99</v>
       </c>
       <c r="D30" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -5365,16 +5302,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>21330051920313</v>
+        <v>21330051920314</v>
       </c>
       <c r="B31" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C31" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="D31" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -5382,16 +5319,16 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>21330051920314</v>
+        <v>21330051920172</v>
       </c>
       <c r="B32" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C32" t="s">
-        <v>103</v>
+        <v>134</v>
       </c>
       <c r="D32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -5399,16 +5336,16 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>21330051920172</v>
+        <v>21330051920315</v>
       </c>
       <c r="B33" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C33" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D33" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -5416,16 +5353,16 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>21330051920315</v>
+        <v>21330051920316</v>
       </c>
       <c r="B34" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C34" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D34" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -5433,16 +5370,16 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>21330051920316</v>
+        <v>21330051920317</v>
       </c>
       <c r="B35" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C35" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D35" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -5450,16 +5387,16 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>21330051920317</v>
+        <v>21330051920318</v>
       </c>
       <c r="B36" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C36" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D36" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -5467,16 +5404,16 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>21330051920318</v>
+        <v>21330051920319</v>
       </c>
       <c r="B37" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C37" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="D37" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -5484,16 +5421,16 @@
     </row>
     <row r="38" spans="1:5">
       <c r="A38">
-        <v>21330051920319</v>
+        <v>21330051920320</v>
       </c>
       <c r="B38" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C38" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="D38" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -5501,16 +5438,16 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39">
-        <v>21330051920320</v>
+        <v>21330051920321</v>
       </c>
       <c r="B39" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C39" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D39" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -5518,16 +5455,16 @@
     </row>
     <row r="40" spans="1:5">
       <c r="A40">
-        <v>21330051920321</v>
+        <v>21330051920323</v>
       </c>
       <c r="B40" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C40" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="D40" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -5535,16 +5472,16 @@
     </row>
     <row r="41" spans="1:5">
       <c r="A41">
-        <v>21330051920323</v>
+        <v>21330051920324</v>
       </c>
       <c r="B41" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C41" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="D41" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -5555,13 +5492,13 @@
         <v>21330051920326</v>
       </c>
       <c r="B42" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C42" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D42" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -5572,13 +5509,13 @@
         <v>21330051920327</v>
       </c>
       <c r="B43" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C43" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D43" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -5589,13 +5526,13 @@
         <v>21330051920328</v>
       </c>
       <c r="B44" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C44" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D44" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -5606,13 +5543,13 @@
         <v>21330051920329</v>
       </c>
       <c r="B45" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C45" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D45" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -5623,13 +5560,13 @@
         <v>21330051920330</v>
       </c>
       <c r="B46" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C46" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D46" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -5677,19 +5614,19 @@
         <v>21330051920303</v>
       </c>
       <c r="B2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5700,13 +5637,13 @@
         <v>21330051920303</v>
       </c>
       <c r="B3" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -5723,13 +5660,13 @@
         <v>21330051920316</v>
       </c>
       <c r="B4" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C4" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -5746,13 +5683,13 @@
         <v>21330051920316</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="D5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -5769,13 +5706,13 @@
         <v>21330051920298</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D6" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -5792,13 +5729,13 @@
         <v>21330051920299</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -5815,13 +5752,13 @@
         <v>21330051920337</v>
       </c>
       <c r="B8" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -5838,13 +5775,13 @@
         <v>21330051920304</v>
       </c>
       <c r="B9" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D9" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
@@ -5861,19 +5798,19 @@
         <v>21330051920305</v>
       </c>
       <c r="B10" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C10" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D10" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5881,22 +5818,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920235</v>
+        <v>21330051920306</v>
       </c>
       <c r="B11" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C11" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="D11" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5904,22 +5841,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920307</v>
+        <v>20330051920235</v>
       </c>
       <c r="B12" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C12" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D12" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -5930,13 +5867,13 @@
         <v>21330051920321</v>
       </c>
       <c r="B13" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C13" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="D13" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -5953,19 +5890,19 @@
         <v>21330051920323</v>
       </c>
       <c r="B14" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="C14" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D14" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -5976,13 +5913,13 @@
         <v>21330051920326</v>
       </c>
       <c r="B15" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C15" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D15" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
@@ -5999,13 +5936,13 @@
         <v>21330051920328</v>
       </c>
       <c r="B16" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C16" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D16" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E16" t="s">
         <v>10</v>
@@ -6022,13 +5959,13 @@
         <v>21330051920330</v>
       </c>
       <c r="B17" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C17" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D17" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>

--- a/grupos/3BLCM - Estadisticos 20221.xlsx
+++ b/grupos/3BLCM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="188">
   <si>
     <t>Materia</t>
   </si>
@@ -221,13 +221,13 @@
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
+    <t>Caballero Rosas María Teresa</t>
+  </si>
+  <si>
+    <t>Ángel Martínez Noe Cristobal</t>
+  </si>
+  <si>
     <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>Caballero Rosas María Teresa</t>
-  </si>
-  <si>
-    <t>Ángel Martínez Noe Cristobal</t>
   </si>
   <si>
     <t>Velasco Sánchez David</t>
@@ -1085,7 +1085,7 @@
         <v>7</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -1100,7 +1100,7 @@
         <v>6</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1136,7 +1136,7 @@
         <v>8</v>
       </c>
       <c r="Y4">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1162,7 +1162,7 @@
         <v>6</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -1177,7 +1177,7 @@
         <v>6</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1198,7 +1198,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U5">
         <v>6</v>
@@ -1213,7 +1213,7 @@
         <v>8</v>
       </c>
       <c r="Y5">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1239,7 +1239,7 @@
         <v>7</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -1254,7 +1254,7 @@
         <v>9</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1290,7 +1290,7 @@
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1316,7 +1316,7 @@
         <v>6</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>-1</v>
@@ -1331,7 +1331,7 @@
         <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1367,7 +1367,7 @@
         <v>10</v>
       </c>
       <c r="Y7">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1393,7 +1393,7 @@
         <v>6</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I8">
         <v>-1</v>
@@ -1408,7 +1408,7 @@
         <v>8</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1429,7 +1429,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U8">
         <v>7</v>
@@ -1444,7 +1444,7 @@
         <v>9</v>
       </c>
       <c r="Y8">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1470,7 +1470,7 @@
         <v>7</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -1485,7 +1485,7 @@
         <v>10</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1547,7 +1547,7 @@
         <v>5</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I10">
         <v>-1</v>
@@ -1562,7 +1562,7 @@
         <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1624,7 +1624,7 @@
         <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -1639,7 +1639,7 @@
         <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1701,7 +1701,7 @@
         <v>5</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -1716,7 +1716,7 @@
         <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1737,7 +1737,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U12">
         <v>8</v>
@@ -1778,7 +1778,7 @@
         <v>5</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -1787,13 +1787,13 @@
         <v>7</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L13">
         <v>6</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1814,7 +1814,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U13">
         <v>7</v>
@@ -1829,7 +1829,7 @@
         <v>7</v>
       </c>
       <c r="Y13">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1855,7 +1855,7 @@
         <v>7</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -1870,7 +1870,7 @@
         <v>6</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1932,7 +1932,7 @@
         <v>6</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -1947,7 +1947,7 @@
         <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1983,7 +1983,7 @@
         <v>10</v>
       </c>
       <c r="Y15">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -2009,7 +2009,7 @@
         <v>5</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -2024,7 +2024,7 @@
         <v>6</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -2060,7 +2060,7 @@
         <v>8</v>
       </c>
       <c r="Y16">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2086,7 +2086,7 @@
         <v>6</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I17">
         <v>-1</v>
@@ -2101,7 +2101,7 @@
         <v>6</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2163,7 +2163,7 @@
         <v>7</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
         <v>-1</v>
@@ -2178,7 +2178,7 @@
         <v>6</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2199,7 +2199,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U18">
         <v>6</v>
@@ -2214,7 +2214,7 @@
         <v>8</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2240,7 +2240,7 @@
         <v>5</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I19">
         <v>-1</v>
@@ -2255,7 +2255,7 @@
         <v>8</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2276,7 +2276,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U19">
         <v>6</v>
@@ -2291,7 +2291,7 @@
         <v>7</v>
       </c>
       <c r="Y19">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2317,7 +2317,7 @@
         <v>6</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -2332,7 +2332,7 @@
         <v>6</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2353,7 +2353,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U20">
         <v>7</v>
@@ -2394,7 +2394,7 @@
         <v>6</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -2409,7 +2409,7 @@
         <v>9</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2430,7 +2430,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>7</v>
@@ -2471,7 +2471,7 @@
         <v>6</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -2486,7 +2486,7 @@
         <v>10</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2507,7 +2507,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U22">
         <v>6</v>
@@ -2522,7 +2522,7 @@
         <v>9</v>
       </c>
       <c r="Y22">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2548,7 +2548,7 @@
         <v>5</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I23">
         <v>-1</v>
@@ -2563,7 +2563,7 @@
         <v>6</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2625,7 +2625,7 @@
         <v>8</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -2640,7 +2640,7 @@
         <v>10</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2702,7 +2702,7 @@
         <v>6</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I25">
         <v>-1</v>
@@ -2717,7 +2717,7 @@
         <v>6</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2779,7 +2779,7 @@
         <v>8</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I26">
         <v>-1</v>
@@ -2794,7 +2794,7 @@
         <v>10</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2830,7 +2830,7 @@
         <v>10</v>
       </c>
       <c r="Y26">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2844,10 +2844,10 @@
         <v>6</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P27">
         <v>-1</v>
@@ -2859,7 +2859,7 @@
         <v>7</v>
       </c>
       <c r="W27">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2885,16 +2885,16 @@
         <v>8</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I28">
         <v>-1</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L28">
         <v>10</v>
@@ -2921,13 +2921,13 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U28">
         <v>6</v>
       </c>
       <c r="V28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W28">
         <v>7</v>
@@ -2962,7 +2962,7 @@
         <v>5</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I29">
         <v>-1</v>
@@ -2977,7 +2977,7 @@
         <v>8</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2998,7 +2998,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U29">
         <v>6</v>
@@ -3039,7 +3039,7 @@
         <v>5</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I30">
         <v>-1</v>
@@ -3054,7 +3054,7 @@
         <v>6</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3075,7 +3075,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U30">
         <v>5</v>
@@ -3116,7 +3116,7 @@
         <v>7</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -3131,7 +3131,7 @@
         <v>7</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3167,7 +3167,7 @@
         <v>8</v>
       </c>
       <c r="Y31">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3193,7 +3193,7 @@
         <v>7</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -3208,7 +3208,7 @@
         <v>7</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3244,7 +3244,7 @@
         <v>7</v>
       </c>
       <c r="Y32">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3270,7 +3270,7 @@
         <v>7</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -3285,7 +3285,7 @@
         <v>6</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3306,7 +3306,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U33">
         <v>6</v>
@@ -3321,7 +3321,7 @@
         <v>8</v>
       </c>
       <c r="Y33">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3347,7 +3347,7 @@
         <v>7</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -3356,13 +3356,13 @@
         <v>6</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L34">
         <v>7</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3424,7 +3424,7 @@
         <v>7</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -3439,7 +3439,7 @@
         <v>10</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3475,7 +3475,7 @@
         <v>10</v>
       </c>
       <c r="Y35">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3501,7 +3501,7 @@
         <v>5</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I36">
         <v>-1</v>
@@ -3516,7 +3516,7 @@
         <v>6</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3552,7 +3552,7 @@
         <v>5</v>
       </c>
       <c r="Y36">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3578,7 +3578,7 @@
         <v>8</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I37">
         <v>-1</v>
@@ -3593,7 +3593,7 @@
         <v>10</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3629,7 +3629,7 @@
         <v>10</v>
       </c>
       <c r="Y37">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3655,7 +3655,7 @@
         <v>8</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -3670,7 +3670,7 @@
         <v>10</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3706,7 +3706,7 @@
         <v>10</v>
       </c>
       <c r="Y38">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:25">
@@ -3732,7 +3732,7 @@
         <v>8</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I39">
         <v>-1</v>
@@ -3747,7 +3747,7 @@
         <v>7</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3783,7 +3783,7 @@
         <v>8</v>
       </c>
       <c r="Y39">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3809,7 +3809,7 @@
         <v>7</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I40">
         <v>-1</v>
@@ -3824,7 +3824,7 @@
         <v>10</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -3860,7 +3860,7 @@
         <v>10</v>
       </c>
       <c r="Y40">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:25">
@@ -3886,7 +3886,7 @@
         <v>5</v>
       </c>
       <c r="H41">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I41">
         <v>-1</v>
@@ -3901,7 +3901,7 @@
         <v>6</v>
       </c>
       <c r="M41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N41">
         <v>-1</v>
@@ -3937,7 +3937,7 @@
         <v>8</v>
       </c>
       <c r="Y41">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -3963,7 +3963,7 @@
         <v>5</v>
       </c>
       <c r="H42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I42">
         <v>-1</v>
@@ -3978,7 +3978,7 @@
         <v>6</v>
       </c>
       <c r="M42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N42">
         <v>-1</v>
@@ -4040,7 +4040,7 @@
         <v>6</v>
       </c>
       <c r="H43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I43">
         <v>-1</v>
@@ -4055,7 +4055,7 @@
         <v>6</v>
       </c>
       <c r="M43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N43">
         <v>-1</v>
@@ -4091,7 +4091,7 @@
         <v>6</v>
       </c>
       <c r="Y43">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -4117,7 +4117,7 @@
         <v>5</v>
       </c>
       <c r="H44">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I44">
         <v>-1</v>
@@ -4132,7 +4132,7 @@
         <v>7</v>
       </c>
       <c r="M44">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N44">
         <v>-1</v>
@@ -4153,7 +4153,7 @@
         <v>-1</v>
       </c>
       <c r="T44">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U44">
         <v>9</v>
@@ -4194,7 +4194,7 @@
         <v>6</v>
       </c>
       <c r="H45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I45">
         <v>-1</v>
@@ -4209,7 +4209,7 @@
         <v>9</v>
       </c>
       <c r="M45">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N45">
         <v>-1</v>
@@ -4271,7 +4271,7 @@
         <v>5</v>
       </c>
       <c r="H46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I46">
         <v>-1</v>
@@ -4286,7 +4286,7 @@
         <v>9</v>
       </c>
       <c r="M46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N46">
         <v>-1</v>
@@ -4348,7 +4348,7 @@
         <v>7</v>
       </c>
       <c r="H47">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I47">
         <v>-1</v>
@@ -4363,7 +4363,7 @@
         <v>9</v>
       </c>
       <c r="M47">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N47">
         <v>-1</v>
@@ -4425,7 +4425,7 @@
         <v>6</v>
       </c>
       <c r="H48">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I48">
         <v>-1</v>
@@ -4440,7 +4440,7 @@
         <v>6</v>
       </c>
       <c r="M48">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N48">
         <v>-1</v>
@@ -4541,19 +4541,19 @@
         <v>44</v>
       </c>
       <c r="D2">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E2">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>70.45</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="G2">
-        <v>29.55</v>
+        <v>18.18</v>
       </c>
       <c r="H2">
-        <v>6.3</v>
+        <v>6.8</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4564,13 +4564,13 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
       </c>
       <c r="C3">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D3">
         <v>39</v>
@@ -4579,24 +4579,24 @@
         <v>5</v>
       </c>
       <c r="F3">
-        <v>88.64</v>
+        <v>86.67</v>
       </c>
       <c r="G3">
-        <v>11.36</v>
+        <v>11.11</v>
       </c>
       <c r="H3">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3">
-        <v>0</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
@@ -4605,51 +4605,51 @@
         <v>45</v>
       </c>
       <c r="D4">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>88.89</v>
+        <v>86.67</v>
       </c>
       <c r="G4">
-        <v>8.890000000000001</v>
+        <v>13.33</v>
       </c>
       <c r="H4">
         <v>7.4</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>2.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>69</v>
       </c>
       <c r="C5">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D5">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E5">
         <v>5</v>
       </c>
       <c r="F5">
-        <v>88.89</v>
+        <v>88.64</v>
       </c>
       <c r="G5">
-        <v>11.11</v>
+        <v>11.36</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4773,7 +4773,7 @@
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -5579,7 +5579,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5611,22 +5611,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920303</v>
+        <v>21330051920298</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C2" t="s">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="D2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5646,10 +5646,10 @@
         <v>160</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5657,22 +5657,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920316</v>
+        <v>21330051920304</v>
       </c>
       <c r="B4" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="C4" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
       <c r="D4" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5680,22 +5680,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920316</v>
+        <v>21330051920305</v>
       </c>
       <c r="B5" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="C5" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="D5" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5703,22 +5703,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920298</v>
+        <v>21330051920306</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="D6" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5726,16 +5726,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920299</v>
+        <v>20330051920235</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C7" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="D7" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920337</v>
+        <v>19330051920208</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="D8" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5772,19 +5772,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920304</v>
+        <v>21330051920308</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C9" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D9" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
         <v>67</v>
@@ -5795,19 +5795,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920305</v>
+        <v>21330051920316</v>
       </c>
       <c r="B10" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="C10" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="D10" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
         <v>69</v>
@@ -5818,19 +5818,19 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920306</v>
+        <v>21330051920323</v>
       </c>
       <c r="B11" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="C11" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="D11" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
         <v>68</v>
@@ -5841,16 +5841,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920235</v>
+        <v>21330051920326</v>
       </c>
       <c r="B12" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="C12" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="D12" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -5864,16 +5864,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920321</v>
+        <v>21330051920328</v>
       </c>
       <c r="B13" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C13" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D13" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -5887,93 +5887,24 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>21330051920323</v>
+        <v>21330051920330</v>
       </c>
       <c r="B14" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C14" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="D14" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
         <v>69</v>
       </c>
       <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920326</v>
-      </c>
-      <c r="B15" t="s">
-        <v>113</v>
-      </c>
-      <c r="C15" t="s">
-        <v>109</v>
-      </c>
-      <c r="D15" t="s">
-        <v>183</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>66</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920328</v>
-      </c>
-      <c r="B16" t="s">
-        <v>115</v>
-      </c>
-      <c r="C16" t="s">
-        <v>142</v>
-      </c>
-      <c r="D16" t="s">
-        <v>185</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>66</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>21330051920330</v>
-      </c>
-      <c r="B17" t="s">
-        <v>117</v>
-      </c>
-      <c r="C17" t="s">
-        <v>144</v>
-      </c>
-      <c r="D17" t="s">
-        <v>187</v>
-      </c>
-      <c r="E17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" t="s">
-        <v>67</v>
-      </c>
-      <c r="G17">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3BLCM - Estadisticos 20221.xlsx
+++ b/grupos/3BLCM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="188">
   <si>
     <t>Materia</t>
   </si>
@@ -221,6 +221,9 @@
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
     <t>Caballero Rosas María Teresa</t>
   </si>
   <si>
@@ -228,9 +231,6 @@
   </si>
   <si>
     <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
-    <t>Velasco Sánchez David</t>
   </si>
   <si>
     <t>Flores González Ángel</t>
@@ -1088,7 +1088,7 @@
         <v>9</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J4">
         <v>8</v>
@@ -1165,7 +1165,7 @@
         <v>9</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J5">
         <v>6</v>
@@ -1201,7 +1201,7 @@
         <v>9</v>
       </c>
       <c r="U5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V5">
         <v>7</v>
@@ -1242,7 +1242,7 @@
         <v>9</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J6">
         <v>7</v>
@@ -1319,7 +1319,7 @@
         <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
         <v>7</v>
@@ -1355,7 +1355,7 @@
         <v>9</v>
       </c>
       <c r="U7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V7">
         <v>8</v>
@@ -1396,7 +1396,7 @@
         <v>9</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
         <v>7</v>
@@ -1432,7 +1432,7 @@
         <v>9</v>
       </c>
       <c r="U8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -1473,7 +1473,7 @@
         <v>9</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J9">
         <v>8</v>
@@ -1550,7 +1550,7 @@
         <v>5</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J10">
         <v>5</v>
@@ -1627,7 +1627,7 @@
         <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
         <v>7</v>
@@ -1704,7 +1704,7 @@
         <v>6</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J12">
         <v>7</v>
@@ -1781,7 +1781,7 @@
         <v>6</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J13">
         <v>7</v>
@@ -1817,7 +1817,7 @@
         <v>8</v>
       </c>
       <c r="U13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V13">
         <v>7</v>
@@ -1858,7 +1858,7 @@
         <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J14">
         <v>8</v>
@@ -1935,7 +1935,7 @@
         <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J15">
         <v>7</v>
@@ -2012,7 +2012,7 @@
         <v>7</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
         <v>6</v>
@@ -2048,7 +2048,7 @@
         <v>7</v>
       </c>
       <c r="U16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V16">
         <v>7</v>
@@ -2089,7 +2089,7 @@
         <v>9</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J17">
         <v>7</v>
@@ -2125,7 +2125,7 @@
         <v>10</v>
       </c>
       <c r="U17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V17">
         <v>8</v>
@@ -2166,7 +2166,7 @@
         <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J18">
         <v>8</v>
@@ -2202,7 +2202,7 @@
         <v>10</v>
       </c>
       <c r="U18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>8</v>
@@ -2243,7 +2243,7 @@
         <v>8</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J19">
         <v>5</v>
@@ -2279,7 +2279,7 @@
         <v>9</v>
       </c>
       <c r="U19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V19">
         <v>5</v>
@@ -2320,7 +2320,7 @@
         <v>7</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J20">
         <v>7</v>
@@ -2397,7 +2397,7 @@
         <v>7</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
         <v>6</v>
@@ -2474,7 +2474,7 @@
         <v>9</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J22">
         <v>5</v>
@@ -2510,7 +2510,7 @@
         <v>9</v>
       </c>
       <c r="U22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V22">
         <v>5</v>
@@ -2551,7 +2551,7 @@
         <v>7</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J23">
         <v>8</v>
@@ -2628,7 +2628,7 @@
         <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J24">
         <v>8</v>
@@ -2664,7 +2664,7 @@
         <v>10</v>
       </c>
       <c r="U24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V24">
         <v>8</v>
@@ -2705,7 +2705,7 @@
         <v>9</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J25">
         <v>6</v>
@@ -2782,7 +2782,7 @@
         <v>8</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J26">
         <v>7</v>
@@ -2818,7 +2818,7 @@
         <v>9</v>
       </c>
       <c r="U26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V26">
         <v>8</v>
@@ -2888,7 +2888,7 @@
         <v>5</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J28">
         <v>5</v>
@@ -2900,7 +2900,7 @@
         <v>10</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2924,7 +2924,7 @@
         <v>7</v>
       </c>
       <c r="U28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V28">
         <v>5</v>
@@ -2936,7 +2936,7 @@
         <v>10</v>
       </c>
       <c r="Y28">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2965,7 +2965,7 @@
         <v>8</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J29">
         <v>-1</v>
@@ -3001,7 +3001,7 @@
         <v>7</v>
       </c>
       <c r="U29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V29">
         <v>-1</v>
@@ -3042,7 +3042,7 @@
         <v>8</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J30">
         <v>5</v>
@@ -3119,7 +3119,7 @@
         <v>9</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J31">
         <v>8</v>
@@ -3155,7 +3155,7 @@
         <v>10</v>
       </c>
       <c r="U31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V31">
         <v>9</v>
@@ -3196,7 +3196,7 @@
         <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J32">
         <v>8</v>
@@ -3232,7 +3232,7 @@
         <v>10</v>
       </c>
       <c r="U32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V32">
         <v>7</v>
@@ -3273,7 +3273,7 @@
         <v>8</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J33">
         <v>6</v>
@@ -3309,7 +3309,7 @@
         <v>9</v>
       </c>
       <c r="U33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V33">
         <v>6</v>
@@ -3350,7 +3350,7 @@
         <v>8</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J34">
         <v>6</v>
@@ -3427,7 +3427,7 @@
         <v>10</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J35">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>10</v>
       </c>
       <c r="U35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V35">
         <v>8</v>
@@ -3504,7 +3504,7 @@
         <v>8</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J36">
         <v>7</v>
@@ -3581,7 +3581,7 @@
         <v>10</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J37">
         <v>7</v>
@@ -3617,7 +3617,7 @@
         <v>10</v>
       </c>
       <c r="U37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V37">
         <v>8</v>
@@ -3658,7 +3658,7 @@
         <v>10</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J38">
         <v>8</v>
@@ -3694,7 +3694,7 @@
         <v>10</v>
       </c>
       <c r="U38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V38">
         <v>9</v>
@@ -3735,7 +3735,7 @@
         <v>8</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J39">
         <v>6</v>
@@ -3812,7 +3812,7 @@
         <v>10</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J40">
         <v>7</v>
@@ -3848,7 +3848,7 @@
         <v>10</v>
       </c>
       <c r="U40">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V40">
         <v>8</v>
@@ -3889,7 +3889,7 @@
         <v>10</v>
       </c>
       <c r="I41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J41">
         <v>8</v>
@@ -3925,7 +3925,7 @@
         <v>10</v>
       </c>
       <c r="U41">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V41">
         <v>8</v>
@@ -3966,7 +3966,7 @@
         <v>6</v>
       </c>
       <c r="I42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J42">
         <v>6</v>
@@ -4043,7 +4043,7 @@
         <v>7</v>
       </c>
       <c r="I43">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J43">
         <v>6</v>
@@ -4079,7 +4079,7 @@
         <v>8</v>
       </c>
       <c r="U43">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V43">
         <v>7</v>
@@ -4120,7 +4120,7 @@
         <v>10</v>
       </c>
       <c r="I44">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J44">
         <v>8</v>
@@ -4197,7 +4197,7 @@
         <v>10</v>
       </c>
       <c r="I45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J45">
         <v>7</v>
@@ -4274,7 +4274,7 @@
         <v>9</v>
       </c>
       <c r="I46">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J46">
         <v>5</v>
@@ -4351,7 +4351,7 @@
         <v>9</v>
       </c>
       <c r="I47">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J47">
         <v>7</v>
@@ -4428,7 +4428,7 @@
         <v>9</v>
       </c>
       <c r="I48">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J48">
         <v>7</v>
@@ -4564,39 +4564,39 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
       </c>
       <c r="C3">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>86.67</v>
+        <v>86.36</v>
       </c>
       <c r="G3">
-        <v>11.11</v>
+        <v>13.64</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>2.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
@@ -4608,48 +4608,48 @@
         <v>39</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4">
         <v>86.67</v>
       </c>
       <c r="G4">
-        <v>13.33</v>
+        <v>11.11</v>
       </c>
       <c r="H4">
         <v>7.4</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>69</v>
       </c>
       <c r="C5">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D5">
         <v>39</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5">
-        <v>88.64</v>
+        <v>86.67</v>
       </c>
       <c r="G5">
-        <v>11.36</v>
+        <v>13.33</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4660,7 +4660,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>70</v>
@@ -4669,19 +4669,19 @@
         <v>44</v>
       </c>
       <c r="D6">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>93.18000000000001</v>
+        <v>88.64</v>
       </c>
       <c r="G6">
-        <v>6.82</v>
+        <v>11.36</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>7.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4773,7 +4773,7 @@
         <v>7</v>
       </c>
       <c r="F2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -5579,7 +5579,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5611,22 +5611,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920298</v>
+        <v>21330051920308</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="C2" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="D2" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5634,22 +5634,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920303</v>
+        <v>21330051920308</v>
       </c>
       <c r="B3" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s">
-        <v>91</v>
+        <v>132</v>
       </c>
       <c r="D3" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5657,22 +5657,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920304</v>
+        <v>21330051920323</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="C4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D4" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5680,22 +5680,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920305</v>
+        <v>21330051920323</v>
       </c>
       <c r="B5" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="C5" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D5" t="s">
-        <v>162</v>
+        <v>181</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5703,22 +5703,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920306</v>
+        <v>21330051920298</v>
       </c>
       <c r="B6" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="D6" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -5726,22 +5726,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920235</v>
+        <v>21330051920303</v>
       </c>
       <c r="B7" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>129</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920208</v>
+        <v>21330051920304</v>
       </c>
       <c r="B8" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C8" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D8" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5772,22 +5772,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920308</v>
+        <v>21330051920305</v>
       </c>
       <c r="B9" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C9" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="D9" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5795,22 +5795,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920316</v>
+        <v>21330051920306</v>
       </c>
       <c r="B10" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="C10" t="s">
-        <v>136</v>
+        <v>109</v>
       </c>
       <c r="D10" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5818,22 +5818,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920323</v>
+        <v>20330051920235</v>
       </c>
       <c r="B11" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="C11" t="s">
         <v>129</v>
       </c>
       <c r="D11" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5841,22 +5841,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920326</v>
+        <v>19330051920208</v>
       </c>
       <c r="B12" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="C12" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="D12" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -5864,22 +5864,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920328</v>
+        <v>21330051920316</v>
       </c>
       <c r="B13" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C13" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="D13" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -5887,24 +5887,70 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
+        <v>21330051920326</v>
+      </c>
+      <c r="B14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C14" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" t="s">
+        <v>183</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
+        <v>66</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920328</v>
+      </c>
+      <c r="B15" t="s">
+        <v>115</v>
+      </c>
+      <c r="C15" t="s">
+        <v>142</v>
+      </c>
+      <c r="D15" t="s">
+        <v>185</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>66</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
         <v>21330051920330</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B16" t="s">
         <v>117</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C16" t="s">
         <v>144</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D16" t="s">
         <v>187</v>
       </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>69</v>
-      </c>
-      <c r="G14">
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>70</v>
+      </c>
+      <c r="G16">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3BLCM - Estadisticos 20221.xlsx
+++ b/grupos/3BLCM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="188">
   <si>
     <t>Materia</t>
   </si>
@@ -248,289 +248,289 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>BALDERAS</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>CHICO</t>
+  </si>
+  <si>
+    <t>DOMINGUEZ</t>
+  </si>
+  <si>
+    <t>DOLORES</t>
+  </si>
+  <si>
+    <t>FRANCO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>JUSTO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>MOTA</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>MOLOHUA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
     <t>OFICIAL</t>
   </si>
   <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
+    <t>PANZO</t>
+  </si>
+  <si>
+    <t>PALAFOX</t>
+  </si>
+  <si>
+    <t>PASTRANA</t>
+  </si>
+  <si>
+    <t>PALOMARES</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
+    <t>PLIEGO</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZUÑIGA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>GAMBINO</t>
+  </si>
+  <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>GIL</t>
+  </si>
+  <si>
+    <t>TINOCO</t>
+  </si>
+  <si>
+    <t>MATA</t>
+  </si>
+  <si>
+    <t>TIBURCIO</t>
+  </si>
+  <si>
+    <t>MONTERO</t>
+  </si>
+  <si>
+    <t>NEGRETE</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>CERON</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>VILLASEÑOR</t>
   </si>
   <si>
+    <t>PAZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>MONGE</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>FLOURENS</t>
+  </si>
+  <si>
+    <t>LIMON</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>VENEGAS</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>ESPINDOLA</t>
+  </si>
+  <si>
+    <t>ANDRES</t>
+  </si>
+  <si>
+    <t>JAZMIN</t>
+  </si>
+  <si>
+    <t>RUTH</t>
+  </si>
+  <si>
+    <t>AXEL EDUARDO</t>
+  </si>
+  <si>
+    <t>VANESSA</t>
+  </si>
+  <si>
+    <t>CARLOS EMILIO</t>
+  </si>
+  <si>
+    <t>PERLA</t>
+  </si>
+  <si>
+    <t>ATZIRI</t>
+  </si>
+  <si>
+    <t>EDNA</t>
+  </si>
+  <si>
+    <t>AMISADAI</t>
+  </si>
+  <si>
+    <t>ZURISADAI</t>
+  </si>
+  <si>
+    <t>CRISTOPHER</t>
+  </si>
+  <si>
+    <t>AMY JULIET</t>
+  </si>
+  <si>
+    <t>LUIS CARLOS</t>
+  </si>
+  <si>
+    <t>YAMILET MONSERRAT</t>
+  </si>
+  <si>
+    <t>YULIET</t>
+  </si>
+  <si>
+    <t>DARLA MARLENE</t>
+  </si>
+  <si>
+    <t>MARIA MICHELLE</t>
+  </si>
+  <si>
+    <t>ANETTE JOCELYN</t>
+  </si>
+  <si>
+    <t>JOSE RAFAEL</t>
+  </si>
+  <si>
+    <t>DIANA CRISTINA</t>
+  </si>
+  <si>
+    <t>NAHOMY</t>
+  </si>
+  <si>
+    <t>ANGEL DIEGO</t>
+  </si>
+  <si>
+    <t>ADAL</t>
+  </si>
+  <si>
+    <t>OLIVA</t>
+  </si>
+  <si>
+    <t>SAIRA LEILANI</t>
+  </si>
+  <si>
     <t>MONICA AIME</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>BALDERAS</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>CHICO</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>DOLORES</t>
-  </si>
-  <si>
-    <t>FRANCO</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>JUSTO</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MORENO</t>
-  </si>
-  <si>
-    <t>MOTA</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>MOLOHUA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>PALAFOX</t>
-  </si>
-  <si>
-    <t>PASTRANA</t>
-  </si>
-  <si>
-    <t>PALOMARES</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>PLIEGO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ZUÑIGA</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>GAMBINO</t>
-  </si>
-  <si>
-    <t>CID</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>GIL</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>MATA</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>MONTERO</t>
-  </si>
-  <si>
-    <t>NEGRETE</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>MONGE</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>FLOURENS</t>
-  </si>
-  <si>
-    <t>LIMON</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>VENEGAS</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>ESPINDOLA</t>
-  </si>
-  <si>
-    <t>ANDRES</t>
-  </si>
-  <si>
-    <t>JAZMIN</t>
-  </si>
-  <si>
-    <t>RUTH</t>
-  </si>
-  <si>
-    <t>AXEL EDUARDO</t>
-  </si>
-  <si>
-    <t>VANESSA</t>
-  </si>
-  <si>
-    <t>CARLOS EMILIO</t>
-  </si>
-  <si>
-    <t>PERLA</t>
-  </si>
-  <si>
-    <t>ATZIRI</t>
-  </si>
-  <si>
-    <t>EDNA</t>
-  </si>
-  <si>
-    <t>AMISADAI</t>
-  </si>
-  <si>
-    <t>ZURISADAI</t>
-  </si>
-  <si>
-    <t>CRISTOPHER</t>
-  </si>
-  <si>
-    <t>AMY JULIET</t>
-  </si>
-  <si>
-    <t>LUIS CARLOS</t>
-  </si>
-  <si>
-    <t>YAMILET MONSERRAT</t>
-  </si>
-  <si>
-    <t>YULIET</t>
-  </si>
-  <si>
-    <t>DARLA MARLENE</t>
-  </si>
-  <si>
-    <t>MARIA MICHELLE</t>
-  </si>
-  <si>
-    <t>ANETTE JOCELYN</t>
-  </si>
-  <si>
-    <t>JOSE RAFAEL</t>
-  </si>
-  <si>
-    <t>DIANA CRISTINA</t>
-  </si>
-  <si>
-    <t>NAHOMY</t>
-  </si>
-  <si>
-    <t>ANGEL DIEGO</t>
-  </si>
-  <si>
-    <t>ADAL</t>
-  </si>
-  <si>
-    <t>OLIVA</t>
-  </si>
-  <si>
-    <t>SAIRA LEILANI</t>
   </si>
   <si>
     <t>ARACELY</t>
@@ -2950,7 +2950,7 @@
         <v>6</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E29">
         <v>5</v>
@@ -2968,7 +2968,7 @@
         <v>5</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K29">
         <v>5</v>
@@ -3004,7 +3004,7 @@
         <v>5</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W29">
         <v>5</v>
@@ -4608,22 +4608,22 @@
         <v>39</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4">
         <v>86.67</v>
       </c>
       <c r="G4">
-        <v>11.11</v>
+        <v>13.33</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>2.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -4729,7 +4729,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4754,26 +4754,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920311</v>
-      </c>
-      <c r="B2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -4809,30 +4789,30 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920311</v>
+        <v>21330051920289</v>
       </c>
       <c r="B2" t="s">
         <v>76</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>112</v>
       </c>
       <c r="D2" t="s">
-        <v>78</v>
+        <v>144</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920289</v>
+        <v>21330051920290</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D3" t="s">
         <v>145</v>
@@ -4843,13 +4823,13 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920290</v>
+        <v>21330051920291</v>
       </c>
       <c r="B4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D4" t="s">
         <v>146</v>
@@ -4860,13 +4840,13 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920291</v>
+        <v>21330051920292</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D5" t="s">
         <v>147</v>
@@ -4877,13 +4857,13 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920292</v>
+        <v>21330051920293</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="D6" t="s">
         <v>148</v>
@@ -4894,13 +4874,13 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920293</v>
+        <v>21330051920294</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="D7" t="s">
         <v>149</v>
@@ -4911,13 +4891,13 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920294</v>
+        <v>21330051920295</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D8" t="s">
         <v>150</v>
@@ -4928,13 +4908,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920295</v>
+        <v>21330051920296</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D9" t="s">
         <v>151</v>
@@ -4945,13 +4925,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051920296</v>
+        <v>21330051920297</v>
       </c>
       <c r="B10" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
-        <v>123</v>
+        <v>76</v>
       </c>
       <c r="D10" t="s">
         <v>152</v>
@@ -4962,13 +4942,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920297</v>
+        <v>21330051920298</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="D11" t="s">
         <v>153</v>
@@ -4979,13 +4959,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920298</v>
+        <v>21330051920299</v>
       </c>
       <c r="B12" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D12" t="s">
         <v>154</v>
@@ -4996,13 +4976,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920299</v>
+        <v>21330051920337</v>
       </c>
       <c r="B13" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="D13" t="s">
         <v>155</v>
@@ -5013,13 +4993,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920337</v>
+        <v>21330051920300</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="D14" t="s">
         <v>156</v>
@@ -5030,13 +5010,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920300</v>
+        <v>21330051920301</v>
       </c>
       <c r="B15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D15" t="s">
         <v>157</v>
@@ -5047,13 +5027,13 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>21330051920301</v>
+        <v>21330051920302</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C16" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D16" t="s">
         <v>158</v>
@@ -5064,13 +5044,13 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>21330051920302</v>
+        <v>21330051920303</v>
       </c>
       <c r="B17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C17" t="s">
-        <v>126</v>
+        <v>88</v>
       </c>
       <c r="D17" t="s">
         <v>159</v>
@@ -5081,13 +5061,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>21330051920303</v>
+        <v>21330051920304</v>
       </c>
       <c r="B18" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C18" t="s">
-        <v>91</v>
+        <v>125</v>
       </c>
       <c r="D18" t="s">
         <v>160</v>
@@ -5098,13 +5078,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>21330051920304</v>
+        <v>21330051920305</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C19" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D19" t="s">
         <v>161</v>
@@ -5115,13 +5095,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>21330051920305</v>
+        <v>21330051920306</v>
       </c>
       <c r="B20" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C20" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="D20" t="s">
         <v>162</v>
@@ -5132,13 +5112,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>21330051920306</v>
+        <v>20330051920235</v>
       </c>
       <c r="B21" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C21" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="D21" t="s">
         <v>163</v>
@@ -5149,13 +5129,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920235</v>
+        <v>21330051920307</v>
       </c>
       <c r="B22" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C22" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D22" t="s">
         <v>164</v>
@@ -5166,13 +5146,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>21330051920307</v>
+        <v>19330051920208</v>
       </c>
       <c r="B23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C23" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D23" t="s">
         <v>165</v>
@@ -5183,13 +5163,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>19330051920208</v>
+        <v>21330051920308</v>
       </c>
       <c r="B24" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C24" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D24" t="s">
         <v>166</v>
@@ -5200,13 +5180,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>21330051920308</v>
+        <v>21330051920309</v>
       </c>
       <c r="B25" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C25" t="s">
-        <v>132</v>
+        <v>101</v>
       </c>
       <c r="D25" t="s">
         <v>167</v>
@@ -5217,13 +5197,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>21330051920309</v>
+        <v>21330051920090</v>
       </c>
       <c r="B26" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C26" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="D26" t="s">
         <v>168</v>
@@ -5234,13 +5214,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>21330051920090</v>
+        <v>21330051920310</v>
       </c>
       <c r="B27" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C27" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D27" t="s">
         <v>169</v>
@@ -5251,13 +5231,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>21330051920310</v>
+        <v>21330051920311</v>
       </c>
       <c r="B28" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C28" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D28" t="s">
         <v>170</v>
@@ -5271,10 +5251,10 @@
         <v>21330051920312</v>
       </c>
       <c r="B29" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C29" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D29" t="s">
         <v>171</v>
@@ -5288,10 +5268,10 @@
         <v>21330051920313</v>
       </c>
       <c r="B30" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C30" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D30" t="s">
         <v>172</v>
@@ -5305,10 +5285,10 @@
         <v>21330051920314</v>
       </c>
       <c r="B31" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C31" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D31" t="s">
         <v>173</v>
@@ -5322,10 +5302,10 @@
         <v>21330051920172</v>
       </c>
       <c r="B32" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C32" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D32" t="s">
         <v>174</v>
@@ -5339,10 +5319,10 @@
         <v>21330051920315</v>
       </c>
       <c r="B33" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C33" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D33" t="s">
         <v>175</v>
@@ -5356,10 +5336,10 @@
         <v>21330051920316</v>
       </c>
       <c r="B34" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C34" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D34" t="s">
         <v>172</v>
@@ -5373,10 +5353,10 @@
         <v>21330051920317</v>
       </c>
       <c r="B35" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C35" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D35" t="s">
         <v>176</v>
@@ -5390,10 +5370,10 @@
         <v>21330051920318</v>
       </c>
       <c r="B36" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C36" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D36" t="s">
         <v>177</v>
@@ -5407,10 +5387,10 @@
         <v>21330051920319</v>
       </c>
       <c r="B37" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C37" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D37" t="s">
         <v>178</v>
@@ -5424,10 +5404,10 @@
         <v>21330051920320</v>
       </c>
       <c r="B38" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C38" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D38" t="s">
         <v>179</v>
@@ -5441,10 +5421,10 @@
         <v>21330051920321</v>
       </c>
       <c r="B39" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C39" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D39" t="s">
         <v>180</v>
@@ -5458,10 +5438,10 @@
         <v>21330051920323</v>
       </c>
       <c r="B40" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C40" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D40" t="s">
         <v>181</v>
@@ -5475,10 +5455,10 @@
         <v>21330051920324</v>
       </c>
       <c r="B41" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C41" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D41" t="s">
         <v>182</v>
@@ -5492,10 +5472,10 @@
         <v>21330051920326</v>
       </c>
       <c r="B42" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C42" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D42" t="s">
         <v>183</v>
@@ -5509,10 +5489,10 @@
         <v>21330051920327</v>
       </c>
       <c r="B43" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C43" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D43" t="s">
         <v>184</v>
@@ -5526,10 +5506,10 @@
         <v>21330051920328</v>
       </c>
       <c r="B44" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C44" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D44" t="s">
         <v>185</v>
@@ -5543,10 +5523,10 @@
         <v>21330051920329</v>
       </c>
       <c r="B45" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C45" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D45" t="s">
         <v>186</v>
@@ -5560,10 +5540,10 @@
         <v>21330051920330</v>
       </c>
       <c r="B46" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C46" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D46" t="s">
         <v>187</v>
@@ -5614,13 +5594,13 @@
         <v>21330051920308</v>
       </c>
       <c r="B2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -5637,13 +5617,13 @@
         <v>21330051920308</v>
       </c>
       <c r="B3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -5660,10 +5640,10 @@
         <v>21330051920323</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D4" t="s">
         <v>181</v>
@@ -5683,10 +5663,10 @@
         <v>21330051920323</v>
       </c>
       <c r="B5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D5" t="s">
         <v>181</v>
@@ -5706,13 +5686,13 @@
         <v>21330051920298</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -5729,13 +5709,13 @@
         <v>21330051920303</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -5752,13 +5732,13 @@
         <v>21330051920304</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
@@ -5775,13 +5755,13 @@
         <v>21330051920305</v>
       </c>
       <c r="B9" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C9" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -5798,13 +5778,13 @@
         <v>21330051920306</v>
       </c>
       <c r="B10" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D10" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
@@ -5821,13 +5801,13 @@
         <v>20330051920235</v>
       </c>
       <c r="B11" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -5844,13 +5824,13 @@
         <v>19330051920208</v>
       </c>
       <c r="B12" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -5867,10 +5847,10 @@
         <v>21330051920316</v>
       </c>
       <c r="B13" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C13" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D13" t="s">
         <v>172</v>
@@ -5890,10 +5870,10 @@
         <v>21330051920326</v>
       </c>
       <c r="B14" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C14" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D14" t="s">
         <v>183</v>
@@ -5913,10 +5893,10 @@
         <v>21330051920328</v>
       </c>
       <c r="B15" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C15" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D15" t="s">
         <v>185</v>
@@ -5936,10 +5916,10 @@
         <v>21330051920330</v>
       </c>
       <c r="B16" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C16" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D16" t="s">
         <v>187</v>

--- a/grupos/3BLCM - Estadisticos 20221.xlsx
+++ b/grupos/3BLCM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="188">
   <si>
     <t>Materia</t>
   </si>
@@ -1115,7 +1115,7 @@
         <v>-1</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -1192,7 +1192,7 @@
         <v>-1</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -1210,7 +1210,7 @@
         <v>8</v>
       </c>
       <c r="X5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y5">
         <v>7</v>
@@ -1269,7 +1269,7 @@
         <v>-1</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S6">
         <v>-1</v>
@@ -1346,7 +1346,7 @@
         <v>-1</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1364,7 +1364,7 @@
         <v>8</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>7</v>
@@ -1423,7 +1423,7 @@
         <v>-1</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -1500,7 +1500,7 @@
         <v>-1</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1518,7 +1518,7 @@
         <v>7</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y9">
         <v>7</v>
@@ -1577,7 +1577,7 @@
         <v>-1</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1654,7 +1654,7 @@
         <v>-1</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -1731,7 +1731,7 @@
         <v>-1</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -1808,7 +1808,7 @@
         <v>-1</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1826,7 +1826,7 @@
         <v>8</v>
       </c>
       <c r="X13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y13">
         <v>6</v>
@@ -1885,7 +1885,7 @@
         <v>-1</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -1962,7 +1962,7 @@
         <v>-1</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -1980,7 +1980,7 @@
         <v>8</v>
       </c>
       <c r="X15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y15">
         <v>7</v>
@@ -2039,7 +2039,7 @@
         <v>-1</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -2116,7 +2116,7 @@
         <v>-1</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -2134,7 +2134,7 @@
         <v>8</v>
       </c>
       <c r="X17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y17">
         <v>6</v>
@@ -2193,7 +2193,7 @@
         <v>-1</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -2270,7 +2270,7 @@
         <v>-1</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -2347,7 +2347,7 @@
         <v>-1</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S20">
         <v>-1</v>
@@ -2365,7 +2365,7 @@
         <v>7</v>
       </c>
       <c r="X20">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y20">
         <v>6</v>
@@ -2424,7 +2424,7 @@
         <v>-1</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
         <v>-1</v>
@@ -2442,7 +2442,7 @@
         <v>5</v>
       </c>
       <c r="X21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>6</v>
@@ -2501,7 +2501,7 @@
         <v>-1</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S22">
         <v>-1</v>
@@ -2519,7 +2519,7 @@
         <v>7</v>
       </c>
       <c r="X22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y22">
         <v>7</v>
@@ -2578,7 +2578,7 @@
         <v>-1</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S23">
         <v>-1</v>
@@ -2655,7 +2655,7 @@
         <v>-1</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
         <v>-1</v>
@@ -2732,7 +2732,7 @@
         <v>-1</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S25">
         <v>-1</v>
@@ -2809,7 +2809,7 @@
         <v>-1</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
         <v>-1</v>
@@ -2827,7 +2827,7 @@
         <v>9</v>
       </c>
       <c r="X26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y26">
         <v>9</v>
@@ -2915,7 +2915,7 @@
         <v>-1</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
         <v>-1</v>
@@ -2992,7 +2992,7 @@
         <v>-1</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S29">
         <v>-1</v>
@@ -3069,7 +3069,7 @@
         <v>-1</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S30">
         <v>-1</v>
@@ -3146,7 +3146,7 @@
         <v>-1</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S31">
         <v>-1</v>
@@ -3223,7 +3223,7 @@
         <v>-1</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S32">
         <v>-1</v>
@@ -3241,7 +3241,7 @@
         <v>8</v>
       </c>
       <c r="X32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y32">
         <v>8</v>
@@ -3300,7 +3300,7 @@
         <v>-1</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S33">
         <v>-1</v>
@@ -3377,7 +3377,7 @@
         <v>-1</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S34">
         <v>-1</v>
@@ -3395,7 +3395,7 @@
         <v>7</v>
       </c>
       <c r="X34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y34">
         <v>7</v>
@@ -3454,7 +3454,7 @@
         <v>-1</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
         <v>-1</v>
@@ -3531,7 +3531,7 @@
         <v>-1</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S36">
         <v>-1</v>
@@ -3549,7 +3549,7 @@
         <v>8</v>
       </c>
       <c r="X36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y36">
         <v>6</v>
@@ -3608,7 +3608,7 @@
         <v>-1</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S37">
         <v>-1</v>
@@ -3685,7 +3685,7 @@
         <v>-1</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S38">
         <v>-1</v>
@@ -3703,7 +3703,7 @@
         <v>8</v>
       </c>
       <c r="X38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y38">
         <v>9</v>
@@ -3762,7 +3762,7 @@
         <v>-1</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S39">
         <v>-1</v>
@@ -3780,7 +3780,7 @@
         <v>7</v>
       </c>
       <c r="X39">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y39">
         <v>7</v>
@@ -3839,7 +3839,7 @@
         <v>-1</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S40">
         <v>-1</v>
@@ -3916,7 +3916,7 @@
         <v>-1</v>
       </c>
       <c r="R41">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S41">
         <v>-1</v>
@@ -3934,7 +3934,7 @@
         <v>8</v>
       </c>
       <c r="X41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y41">
         <v>7</v>
@@ -3993,7 +3993,7 @@
         <v>-1</v>
       </c>
       <c r="R42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S42">
         <v>-1</v>
@@ -4070,7 +4070,7 @@
         <v>-1</v>
       </c>
       <c r="R43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S43">
         <v>-1</v>
@@ -4147,7 +4147,7 @@
         <v>-1</v>
       </c>
       <c r="R44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S44">
         <v>-1</v>
@@ -4209,7 +4209,7 @@
         <v>9</v>
       </c>
       <c r="M45">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N45">
         <v>-1</v>
@@ -4224,7 +4224,7 @@
         <v>-1</v>
       </c>
       <c r="R45">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S45">
         <v>-1</v>
@@ -4245,7 +4245,7 @@
         <v>9</v>
       </c>
       <c r="Y45">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:25">
@@ -4301,7 +4301,7 @@
         <v>-1</v>
       </c>
       <c r="R46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S46">
         <v>-1</v>
@@ -4363,7 +4363,7 @@
         <v>9</v>
       </c>
       <c r="M47">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N47">
         <v>-1</v>
@@ -4378,7 +4378,7 @@
         <v>-1</v>
       </c>
       <c r="R47">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S47">
         <v>-1</v>
@@ -4399,7 +4399,7 @@
         <v>9</v>
       </c>
       <c r="Y47">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48" spans="1:25">
@@ -4455,7 +4455,7 @@
         <v>-1</v>
       </c>
       <c r="R48">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S48">
         <v>-1</v>
@@ -4473,7 +4473,7 @@
         <v>9</v>
       </c>
       <c r="X48">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y48">
         <v>6</v>
@@ -4553,7 +4553,7 @@
         <v>18.18</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4669,19 +4669,19 @@
         <v>44</v>
       </c>
       <c r="D6">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>88.64</v>
+        <v>95.45</v>
       </c>
       <c r="G6">
-        <v>11.36</v>
+        <v>4.55</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5559,7 +5559,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5729,22 +5729,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920304</v>
+        <v>21330051920305</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5752,22 +5752,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920305</v>
+        <v>21330051920306</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="D9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -5775,22 +5775,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920306</v>
+        <v>20330051920235</v>
       </c>
       <c r="B10" t="s">
         <v>92</v>
       </c>
       <c r="C10" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="D10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5798,22 +5798,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920235</v>
+        <v>19330051920208</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D11" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5821,22 +5821,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920208</v>
+        <v>21330051920326</v>
       </c>
       <c r="B12" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="C12" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="D12" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -5844,93 +5844,24 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920316</v>
+        <v>21330051920328</v>
       </c>
       <c r="B13" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="C13" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="D13" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920326</v>
-      </c>
-      <c r="B14" t="s">
-        <v>111</v>
-      </c>
-      <c r="C14" t="s">
-        <v>107</v>
-      </c>
-      <c r="D14" t="s">
-        <v>183</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>66</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920328</v>
-      </c>
-      <c r="B15" t="s">
-        <v>113</v>
-      </c>
-      <c r="C15" t="s">
-        <v>141</v>
-      </c>
-      <c r="D15" t="s">
-        <v>185</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>66</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>21330051920330</v>
-      </c>
-      <c r="B16" t="s">
-        <v>115</v>
-      </c>
-      <c r="C16" t="s">
-        <v>143</v>
-      </c>
-      <c r="D16" t="s">
-        <v>187</v>
-      </c>
-      <c r="E16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" t="s">
-        <v>70</v>
-      </c>
-      <c r="G16">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3BLCM - Estadisticos 20221.xlsx
+++ b/grupos/3BLCM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="188">
   <si>
     <t>Materia</t>
   </si>
@@ -221,13 +221,13 @@
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
+    <t>Ángel Martínez Noe Cristobal</t>
+  </si>
+  <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
     <t>Caballero Rosas María Teresa</t>
-  </si>
-  <si>
-    <t>Ángel Martínez Noe Cristobal</t>
   </si>
   <si>
     <t>Avila Coronado Julieta</t>
@@ -1109,10 +1109,10 @@
         <v>-1</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R4">
         <v>10</v>
@@ -1186,10 +1186,10 @@
         <v>-1</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R5">
         <v>6</v>
@@ -1204,10 +1204,10 @@
         <v>7</v>
       </c>
       <c r="V5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X5">
         <v>7</v>
@@ -1263,10 +1263,10 @@
         <v>-1</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
         <v>9</v>
@@ -1284,7 +1284,7 @@
         <v>7</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X6">
         <v>9</v>
@@ -1340,10 +1340,10 @@
         <v>-1</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R7">
         <v>8</v>
@@ -1358,10 +1358,10 @@
         <v>7</v>
       </c>
       <c r="V7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X7">
         <v>9</v>
@@ -1417,10 +1417,10 @@
         <v>-1</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R8">
         <v>9</v>
@@ -1435,10 +1435,10 @@
         <v>8</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X8">
         <v>9</v>
@@ -1494,10 +1494,10 @@
         <v>-1</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R9">
         <v>10</v>
@@ -1571,10 +1571,10 @@
         <v>-1</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R10">
         <v>5</v>
@@ -1648,10 +1648,10 @@
         <v>-1</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R11">
         <v>10</v>
@@ -1725,10 +1725,10 @@
         <v>-1</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R12">
         <v>8</v>
@@ -1746,7 +1746,7 @@
         <v>8</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X12">
         <v>8</v>
@@ -1802,10 +1802,10 @@
         <v>-1</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
         <v>9</v>
@@ -1823,7 +1823,7 @@
         <v>7</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X13">
         <v>8</v>
@@ -1879,10 +1879,10 @@
         <v>-1</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R14">
         <v>7</v>
@@ -1897,10 +1897,10 @@
         <v>7</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X14">
         <v>8</v>
@@ -1956,10 +1956,10 @@
         <v>-1</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
         <v>8</v>
@@ -2033,10 +2033,10 @@
         <v>-1</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R16">
         <v>7</v>
@@ -2054,7 +2054,7 @@
         <v>7</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X16">
         <v>8</v>
@@ -2110,10 +2110,10 @@
         <v>-1</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
         <v>10</v>
@@ -2187,10 +2187,10 @@
         <v>-1</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
         <v>7</v>
@@ -2208,7 +2208,7 @@
         <v>8</v>
       </c>
       <c r="W18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X18">
         <v>8</v>
@@ -2264,10 +2264,10 @@
         <v>-1</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
         <v>8</v>
@@ -2282,7 +2282,7 @@
         <v>7</v>
       </c>
       <c r="V19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W19">
         <v>8</v>
@@ -2341,10 +2341,10 @@
         <v>-1</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R20">
         <v>7</v>
@@ -2418,10 +2418,10 @@
         <v>-1</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R21">
         <v>7</v>
@@ -2495,10 +2495,10 @@
         <v>-1</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R22">
         <v>7</v>
@@ -2513,7 +2513,7 @@
         <v>7</v>
       </c>
       <c r="V22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W22">
         <v>7</v>
@@ -2572,10 +2572,10 @@
         <v>-1</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
         <v>9</v>
@@ -2649,10 +2649,10 @@
         <v>-1</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R24">
         <v>9</v>
@@ -2726,10 +2726,10 @@
         <v>-1</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="R25">
         <v>6</v>
@@ -2747,7 +2747,7 @@
         <v>6</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X25">
         <v>6</v>
@@ -2803,10 +2803,10 @@
         <v>-1</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R26">
         <v>9</v>
@@ -2824,7 +2824,7 @@
         <v>8</v>
       </c>
       <c r="W26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X26">
         <v>9</v>
@@ -2850,16 +2850,16 @@
         <v>5</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V27">
         <v>7</v>
       </c>
       <c r="W27">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2909,10 +2909,10 @@
         <v>-1</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="R28">
         <v>10</v>
@@ -2930,7 +2930,7 @@
         <v>5</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X28">
         <v>10</v>
@@ -2986,10 +2986,10 @@
         <v>-1</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R29">
         <v>7</v>
@@ -3063,10 +3063,10 @@
         <v>-1</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R30">
         <v>5</v>
@@ -3084,7 +3084,7 @@
         <v>5</v>
       </c>
       <c r="W30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X30">
         <v>5</v>
@@ -3140,10 +3140,10 @@
         <v>-1</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R31">
         <v>7</v>
@@ -3158,10 +3158,10 @@
         <v>7</v>
       </c>
       <c r="V31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X31">
         <v>8</v>
@@ -3217,10 +3217,10 @@
         <v>-1</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R32">
         <v>6</v>
@@ -3238,7 +3238,7 @@
         <v>7</v>
       </c>
       <c r="W32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X32">
         <v>6</v>
@@ -3294,10 +3294,10 @@
         <v>-1</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R33">
         <v>7</v>
@@ -3312,7 +3312,7 @@
         <v>7</v>
       </c>
       <c r="V33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W33">
         <v>8</v>
@@ -3371,10 +3371,10 @@
         <v>-1</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R34">
         <v>8</v>
@@ -3389,10 +3389,10 @@
         <v>6</v>
       </c>
       <c r="V34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X34">
         <v>8</v>
@@ -3448,10 +3448,10 @@
         <v>-1</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R35">
         <v>10</v>
@@ -3525,10 +3525,10 @@
         <v>-1</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R36">
         <v>8</v>
@@ -3546,7 +3546,7 @@
         <v>7</v>
       </c>
       <c r="W36">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X36">
         <v>6</v>
@@ -3602,10 +3602,10 @@
         <v>-1</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R37">
         <v>10</v>
@@ -3679,10 +3679,10 @@
         <v>-1</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R38">
         <v>7</v>
@@ -3756,10 +3756,10 @@
         <v>-1</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R39">
         <v>6</v>
@@ -3777,7 +3777,7 @@
         <v>7</v>
       </c>
       <c r="W39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X39">
         <v>7</v>
@@ -3833,10 +3833,10 @@
         <v>-1</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R40">
         <v>10</v>
@@ -3910,10 +3910,10 @@
         <v>-1</v>
       </c>
       <c r="P41">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R41">
         <v>7</v>
@@ -3928,7 +3928,7 @@
         <v>8</v>
       </c>
       <c r="V41">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W41">
         <v>8</v>
@@ -3987,10 +3987,10 @@
         <v>-1</v>
       </c>
       <c r="P42">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R42">
         <v>6</v>
@@ -4005,7 +4005,7 @@
         <v>5</v>
       </c>
       <c r="V42">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W42">
         <v>5</v>
@@ -4064,10 +4064,10 @@
         <v>-1</v>
       </c>
       <c r="P43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R43">
         <v>7</v>
@@ -4141,10 +4141,10 @@
         <v>-1</v>
       </c>
       <c r="P44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R44">
         <v>7</v>
@@ -4159,7 +4159,7 @@
         <v>9</v>
       </c>
       <c r="V44">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W44">
         <v>8</v>
@@ -4218,10 +4218,10 @@
         <v>-1</v>
       </c>
       <c r="P45">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R45">
         <v>9</v>
@@ -4239,7 +4239,7 @@
         <v>8</v>
       </c>
       <c r="W45">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X45">
         <v>9</v>
@@ -4295,10 +4295,10 @@
         <v>-1</v>
       </c>
       <c r="P46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R46">
         <v>9</v>
@@ -4313,10 +4313,10 @@
         <v>6</v>
       </c>
       <c r="V46">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W46">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X46">
         <v>9</v>
@@ -4372,10 +4372,10 @@
         <v>-1</v>
       </c>
       <c r="P47">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q47">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R47">
         <v>8</v>
@@ -4449,10 +4449,10 @@
         <v>-1</v>
       </c>
       <c r="P48">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q48">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R48">
         <v>9</v>
@@ -4470,7 +4470,7 @@
         <v>8</v>
       </c>
       <c r="W48">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X48">
         <v>7</v>
@@ -4564,28 +4564,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
       </c>
       <c r="C3">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D3">
         <v>38</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>86.36</v>
+        <v>84.44</v>
       </c>
       <c r="G3">
-        <v>13.64</v>
+        <v>15.56</v>
       </c>
       <c r="H3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4596,28 +4596,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
       </c>
       <c r="C4">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D4">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E4">
         <v>6</v>
       </c>
       <c r="F4">
-        <v>86.67</v>
+        <v>86.36</v>
       </c>
       <c r="G4">
-        <v>13.33</v>
+        <v>13.64</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4628,7 +4628,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>69</v>
@@ -4637,19 +4637,19 @@
         <v>45</v>
       </c>
       <c r="D5">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>86.67</v>
+        <v>88.89</v>
       </c>
       <c r="G5">
-        <v>13.33</v>
+        <v>11.11</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5559,7 +5559,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920308</v>
+        <v>21330051920323</v>
       </c>
       <c r="B2" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D2" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5614,22 +5614,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920308</v>
+        <v>21330051920323</v>
       </c>
       <c r="B3" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="C3" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D3" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5637,19 +5637,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920323</v>
+        <v>21330051920328</v>
       </c>
       <c r="B4" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C4" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
         <v>67</v>
@@ -5660,22 +5660,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920323</v>
+        <v>21330051920328</v>
       </c>
       <c r="B5" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C5" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D5" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5706,22 +5706,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920303</v>
+        <v>21330051920305</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>126</v>
       </c>
       <c r="D7" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5729,22 +5729,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920305</v>
+        <v>20330051920235</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D8" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5752,116 +5752,24 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920306</v>
+        <v>21330051920326</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="C9" t="s">
         <v>107</v>
       </c>
       <c r="D9" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920235</v>
-      </c>
-      <c r="B10" t="s">
-        <v>92</v>
-      </c>
-      <c r="C10" t="s">
-        <v>127</v>
-      </c>
-      <c r="D10" t="s">
-        <v>163</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>66</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>19330051920208</v>
-      </c>
-      <c r="B11" t="s">
-        <v>94</v>
-      </c>
-      <c r="C11" t="s">
-        <v>129</v>
-      </c>
-      <c r="D11" t="s">
-        <v>165</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>69</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920326</v>
-      </c>
-      <c r="B12" t="s">
-        <v>111</v>
-      </c>
-      <c r="C12" t="s">
-        <v>107</v>
-      </c>
-      <c r="D12" t="s">
-        <v>183</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>66</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920328</v>
-      </c>
-      <c r="B13" t="s">
-        <v>113</v>
-      </c>
-      <c r="C13" t="s">
-        <v>141</v>
-      </c>
-      <c r="D13" t="s">
-        <v>185</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>66</v>
-      </c>
-      <c r="G13">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3BLCM - Estadisticos 20221.xlsx
+++ b/grupos/3BLCM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="188">
   <si>
     <t>Materia</t>
   </si>
@@ -1106,7 +1106,7 @@
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P4">
         <v>8</v>
@@ -1183,7 +1183,7 @@
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P5">
         <v>6</v>
@@ -1201,7 +1201,7 @@
         <v>9</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V5">
         <v>6</v>
@@ -1260,7 +1260,7 @@
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
         <v>8</v>
@@ -1337,7 +1337,7 @@
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P7">
         <v>6</v>
@@ -1414,7 +1414,7 @@
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
         <v>7</v>
@@ -1491,7 +1491,7 @@
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
         <v>6</v>
@@ -1568,7 +1568,7 @@
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P10">
         <v>5</v>
@@ -1645,7 +1645,7 @@
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P11">
         <v>8</v>
@@ -1722,7 +1722,7 @@
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
         <v>8</v>
@@ -1817,7 +1817,7 @@
         <v>8</v>
       </c>
       <c r="U13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V13">
         <v>7</v>
@@ -1876,7 +1876,7 @@
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P14">
         <v>7</v>
@@ -1953,7 +1953,7 @@
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
         <v>9</v>
@@ -2030,7 +2030,7 @@
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P16">
         <v>8</v>
@@ -2107,7 +2107,7 @@
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P17">
         <v>8</v>
@@ -2125,7 +2125,7 @@
         <v>10</v>
       </c>
       <c r="U17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V17">
         <v>8</v>
@@ -2184,7 +2184,7 @@
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P18">
         <v>7</v>
@@ -2202,7 +2202,7 @@
         <v>10</v>
       </c>
       <c r="U18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V18">
         <v>8</v>
@@ -2261,7 +2261,7 @@
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P19">
         <v>8</v>
@@ -2338,7 +2338,7 @@
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P20">
         <v>8</v>
@@ -2415,7 +2415,7 @@
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P21">
         <v>6</v>
@@ -2492,7 +2492,7 @@
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
         <v>7</v>
@@ -2510,7 +2510,7 @@
         <v>9</v>
       </c>
       <c r="U22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V22">
         <v>6</v>
@@ -2569,7 +2569,7 @@
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P23">
         <v>7</v>
@@ -2587,7 +2587,7 @@
         <v>7</v>
       </c>
       <c r="U23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>8</v>
@@ -2646,7 +2646,7 @@
         <v>-1</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P24">
         <v>7</v>
@@ -2723,7 +2723,7 @@
         <v>-1</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P25">
         <v>6</v>
@@ -2800,7 +2800,7 @@
         <v>-1</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P26">
         <v>8</v>
@@ -2906,7 +2906,7 @@
         <v>-1</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P28">
         <v>5</v>
@@ -2983,7 +2983,7 @@
         <v>-1</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P29">
         <v>5</v>
@@ -3060,7 +3060,7 @@
         <v>-1</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P30">
         <v>5</v>
@@ -3137,7 +3137,7 @@
         <v>-1</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P31">
         <v>7</v>
@@ -3214,7 +3214,7 @@
         <v>-1</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P32">
         <v>8</v>
@@ -3291,7 +3291,7 @@
         <v>-1</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P33">
         <v>8</v>
@@ -3368,7 +3368,7 @@
         <v>-1</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P34">
         <v>6</v>
@@ -3445,7 +3445,7 @@
         <v>-1</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P35">
         <v>8</v>
@@ -3522,7 +3522,7 @@
         <v>-1</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P36">
         <v>7</v>
@@ -3599,7 +3599,7 @@
         <v>-1</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P37">
         <v>8</v>
@@ -3676,7 +3676,7 @@
         <v>-1</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P38">
         <v>8</v>
@@ -3694,7 +3694,7 @@
         <v>10</v>
       </c>
       <c r="U38">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V38">
         <v>9</v>
@@ -3753,7 +3753,7 @@
         <v>-1</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P39">
         <v>7</v>
@@ -3771,7 +3771,7 @@
         <v>8</v>
       </c>
       <c r="U39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V39">
         <v>7</v>
@@ -3830,7 +3830,7 @@
         <v>-1</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P40">
         <v>8</v>
@@ -3848,7 +3848,7 @@
         <v>10</v>
       </c>
       <c r="U40">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V40">
         <v>8</v>
@@ -3907,7 +3907,7 @@
         <v>-1</v>
       </c>
       <c r="O41">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P41">
         <v>6</v>
@@ -3984,7 +3984,7 @@
         <v>-1</v>
       </c>
       <c r="O42">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P42">
         <v>4</v>
@@ -4061,7 +4061,7 @@
         <v>-1</v>
       </c>
       <c r="O43">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P43">
         <v>7</v>
@@ -4079,7 +4079,7 @@
         <v>8</v>
       </c>
       <c r="U43">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V43">
         <v>7</v>
@@ -4138,7 +4138,7 @@
         <v>-1</v>
       </c>
       <c r="O44">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P44">
         <v>6</v>
@@ -4156,7 +4156,7 @@
         <v>10</v>
       </c>
       <c r="U44">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V44">
         <v>8</v>
@@ -4215,7 +4215,7 @@
         <v>-1</v>
       </c>
       <c r="O45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P45">
         <v>8</v>
@@ -4292,7 +4292,7 @@
         <v>-1</v>
       </c>
       <c r="O46">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P46">
         <v>5</v>
@@ -4369,7 +4369,7 @@
         <v>-1</v>
       </c>
       <c r="O47">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P47">
         <v>8</v>
@@ -4387,7 +4387,7 @@
         <v>9</v>
       </c>
       <c r="U47">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V47">
         <v>8</v>
@@ -4446,7 +4446,7 @@
         <v>-1</v>
       </c>
       <c r="O48">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P48">
         <v>7</v>
@@ -4464,7 +4464,7 @@
         <v>9</v>
       </c>
       <c r="U48">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V48">
         <v>8</v>
@@ -4605,19 +4605,19 @@
         <v>44</v>
       </c>
       <c r="D4">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>86.36</v>
+        <v>88.64</v>
       </c>
       <c r="G4">
-        <v>13.64</v>
+        <v>11.36</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5559,7 +5559,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920323</v>
+        <v>21330051920328</v>
       </c>
       <c r="B2" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C2" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5614,22 +5614,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920323</v>
+        <v>21330051920328</v>
       </c>
       <c r="B3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C3" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="D3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5637,22 +5637,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920328</v>
+        <v>21330051920298</v>
       </c>
       <c r="B4" t="s">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="D4" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5660,22 +5660,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920328</v>
+        <v>21330051920305</v>
       </c>
       <c r="B5" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="D5" t="s">
-        <v>185</v>
+        <v>161</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -5683,16 +5683,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920298</v>
+        <v>20330051920235</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D6" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -5706,16 +5706,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920305</v>
+        <v>21330051920323</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="C7" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D7" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -5729,16 +5729,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920235</v>
+        <v>21330051920326</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="C8" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="D8" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -5747,29 +5747,6 @@
         <v>66</v>
       </c>
       <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920326</v>
-      </c>
-      <c r="B9" t="s">
-        <v>111</v>
-      </c>
-      <c r="C9" t="s">
-        <v>107</v>
-      </c>
-      <c r="D9" t="s">
-        <v>183</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>66</v>
-      </c>
-      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3BLCM - Estadisticos 20221.xlsx
+++ b/grupos/3BLCM - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="188">
   <si>
     <t>Materia</t>
   </si>
@@ -218,13 +218,13 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Ángel Martínez Noe Cristobal</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
     <t>Ochoa Martínez Mayeli</t>
-  </si>
-  <si>
-    <t>Ángel Martínez Noe Cristobal</t>
-  </si>
-  <si>
-    <t>Velasco Sánchez David</t>
   </si>
   <si>
     <t>Caballero Rosas María Teresa</t>
@@ -1118,7 +1118,7 @@
         <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T4">
         <v>9</v>
@@ -1136,7 +1136,7 @@
         <v>8</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1195,7 +1195,7 @@
         <v>6</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T5">
         <v>9</v>
@@ -1213,7 +1213,7 @@
         <v>7</v>
       </c>
       <c r="Y5">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1272,7 +1272,7 @@
         <v>9</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -1290,7 +1290,7 @@
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1349,7 +1349,7 @@
         <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T7">
         <v>9</v>
@@ -1426,7 +1426,7 @@
         <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>9</v>
@@ -1503,7 +1503,7 @@
         <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T9">
         <v>10</v>
@@ -1580,7 +1580,7 @@
         <v>5</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T10">
         <v>5</v>
@@ -1657,7 +1657,7 @@
         <v>10</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
         <v>10</v>
@@ -1734,7 +1734,7 @@
         <v>8</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
         <v>8</v>
@@ -1752,7 +1752,7 @@
         <v>8</v>
       </c>
       <c r="Y12">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1811,7 +1811,7 @@
         <v>9</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T13">
         <v>8</v>
@@ -1829,7 +1829,7 @@
         <v>8</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1888,7 +1888,7 @@
         <v>7</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T14">
         <v>10</v>
@@ -1906,7 +1906,7 @@
         <v>8</v>
       </c>
       <c r="Y14">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1965,7 +1965,7 @@
         <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T15">
         <v>10</v>
@@ -2042,7 +2042,7 @@
         <v>7</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T16">
         <v>7</v>
@@ -2119,7 +2119,7 @@
         <v>10</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
         <v>10</v>
@@ -2196,7 +2196,7 @@
         <v>7</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
         <v>10</v>
@@ -2273,7 +2273,7 @@
         <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T19">
         <v>9</v>
@@ -2350,7 +2350,7 @@
         <v>7</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T20">
         <v>9</v>
@@ -2427,7 +2427,7 @@
         <v>7</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T21">
         <v>8</v>
@@ -2504,7 +2504,7 @@
         <v>7</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
         <v>9</v>
@@ -2581,7 +2581,7 @@
         <v>9</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
         <v>7</v>
@@ -2599,7 +2599,7 @@
         <v>7</v>
       </c>
       <c r="Y23">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2658,7 +2658,7 @@
         <v>9</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T24">
         <v>10</v>
@@ -2676,7 +2676,7 @@
         <v>8</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2735,7 +2735,7 @@
         <v>6</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T25">
         <v>9</v>
@@ -2812,7 +2812,7 @@
         <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T26">
         <v>9</v>
@@ -2830,7 +2830,7 @@
         <v>9</v>
       </c>
       <c r="Y26">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2918,7 +2918,7 @@
         <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T28">
         <v>7</v>
@@ -2936,7 +2936,7 @@
         <v>10</v>
       </c>
       <c r="Y28">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2995,7 +2995,7 @@
         <v>7</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T29">
         <v>7</v>
@@ -3072,7 +3072,7 @@
         <v>5</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T30">
         <v>8</v>
@@ -3149,7 +3149,7 @@
         <v>7</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T31">
         <v>10</v>
@@ -3226,7 +3226,7 @@
         <v>6</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
         <v>10</v>
@@ -3303,7 +3303,7 @@
         <v>7</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T33">
         <v>9</v>
@@ -3380,7 +3380,7 @@
         <v>8</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T34">
         <v>9</v>
@@ -3457,7 +3457,7 @@
         <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T35">
         <v>10</v>
@@ -3534,7 +3534,7 @@
         <v>8</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T36">
         <v>9</v>
@@ -3611,7 +3611,7 @@
         <v>10</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T37">
         <v>10</v>
@@ -3688,7 +3688,7 @@
         <v>7</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T38">
         <v>10</v>
@@ -3765,7 +3765,7 @@
         <v>6</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T39">
         <v>8</v>
@@ -3783,7 +3783,7 @@
         <v>7</v>
       </c>
       <c r="Y39">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3842,7 +3842,7 @@
         <v>10</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T40">
         <v>10</v>
@@ -3919,7 +3919,7 @@
         <v>7</v>
       </c>
       <c r="S41">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T41">
         <v>10</v>
@@ -3937,7 +3937,7 @@
         <v>7</v>
       </c>
       <c r="Y41">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:25">
@@ -3996,7 +3996,7 @@
         <v>6</v>
       </c>
       <c r="S42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T42">
         <v>5</v>
@@ -4073,7 +4073,7 @@
         <v>7</v>
       </c>
       <c r="S43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T43">
         <v>8</v>
@@ -4091,7 +4091,7 @@
         <v>6</v>
       </c>
       <c r="Y43">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:25">
@@ -4150,7 +4150,7 @@
         <v>7</v>
       </c>
       <c r="S44">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T44">
         <v>10</v>
@@ -4168,7 +4168,7 @@
         <v>7</v>
       </c>
       <c r="Y44">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:25">
@@ -4227,7 +4227,7 @@
         <v>9</v>
       </c>
       <c r="S45">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T45">
         <v>10</v>
@@ -4245,7 +4245,7 @@
         <v>9</v>
       </c>
       <c r="Y45">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:25">
@@ -4304,7 +4304,7 @@
         <v>9</v>
       </c>
       <c r="S46">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T46">
         <v>9</v>
@@ -4381,7 +4381,7 @@
         <v>8</v>
       </c>
       <c r="S47">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T47">
         <v>9</v>
@@ -4458,7 +4458,7 @@
         <v>9</v>
       </c>
       <c r="S48">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T48">
         <v>9</v>
@@ -4532,28 +4532,28 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
         <v>66</v>
       </c>
       <c r="C2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>81.81999999999999</v>
+        <v>84.44</v>
       </c>
       <c r="G2">
-        <v>18.18</v>
+        <v>15.56</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4564,25 +4564,25 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>67</v>
       </c>
       <c r="C3">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D3">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>84.44</v>
+        <v>88.64</v>
       </c>
       <c r="G3">
-        <v>15.56</v>
+        <v>11.36</v>
       </c>
       <c r="H3">
         <v>7</v>
@@ -4596,7 +4596,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>68</v>
@@ -4617,7 +4617,7 @@
         <v>11.36</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5559,7 +5559,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5606,7 +5606,7 @@
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5629,7 +5629,7 @@
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5637,19 +5637,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920298</v>
+        <v>21330051920305</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="D4" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
         <v>66</v>
@@ -5660,93 +5660,24 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920305</v>
+        <v>21330051920323</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="C5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D5" t="s">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920235</v>
-      </c>
-      <c r="B6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C6" t="s">
-        <v>127</v>
-      </c>
-      <c r="D6" t="s">
-        <v>163</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>66</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920323</v>
-      </c>
-      <c r="B7" t="s">
-        <v>109</v>
-      </c>
-      <c r="C7" t="s">
-        <v>127</v>
-      </c>
-      <c r="D7" t="s">
-        <v>181</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>67</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920326</v>
-      </c>
-      <c r="B8" t="s">
-        <v>111</v>
-      </c>
-      <c r="C8" t="s">
-        <v>107</v>
-      </c>
-      <c r="D8" t="s">
-        <v>183</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>66</v>
-      </c>
-      <c r="G8">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3BLCM - Estadisticos 20221.xlsx
+++ b/grupos/3BLCM - Estadisticos 20221.xlsx
@@ -1103,7 +1103,7 @@
         <v>8</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
         <v>8</v>
@@ -1180,7 +1180,7 @@
         <v>7</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
         <v>6</v>
@@ -1257,7 +1257,7 @@
         <v>8</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O6">
         <v>7</v>
@@ -1275,7 +1275,7 @@
         <v>5</v>
       </c>
       <c r="T6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U6">
         <v>8</v>
@@ -1334,7 +1334,7 @@
         <v>7</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
         <v>7</v>
@@ -1411,7 +1411,7 @@
         <v>7</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
         <v>8</v>
@@ -1488,7 +1488,7 @@
         <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
         <v>9</v>
@@ -1506,7 +1506,7 @@
         <v>7</v>
       </c>
       <c r="T9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U9">
         <v>9</v>
@@ -1565,7 +1565,7 @@
         <v>5</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O10">
         <v>6</v>
@@ -1642,7 +1642,7 @@
         <v>9</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11">
         <v>8</v>
@@ -1719,7 +1719,7 @@
         <v>6</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O12">
         <v>8</v>
@@ -1796,7 +1796,7 @@
         <v>7</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
         <v>7</v>
@@ -1873,7 +1873,7 @@
         <v>7</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
         <v>8</v>
@@ -1950,7 +1950,7 @@
         <v>8</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O15">
         <v>7</v>
@@ -2027,7 +2027,7 @@
         <v>7</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O16">
         <v>7</v>
@@ -2104,7 +2104,7 @@
         <v>6</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O17">
         <v>6</v>
@@ -2122,7 +2122,7 @@
         <v>7</v>
       </c>
       <c r="T17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U17">
         <v>6</v>
@@ -2181,7 +2181,7 @@
         <v>8</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O18">
         <v>7</v>
@@ -2199,7 +2199,7 @@
         <v>9</v>
       </c>
       <c r="T18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U18">
         <v>7</v>
@@ -2258,7 +2258,7 @@
         <v>7</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
         <v>7</v>
@@ -2335,7 +2335,7 @@
         <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
         <v>7</v>
@@ -2412,7 +2412,7 @@
         <v>6</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O21">
         <v>7</v>
@@ -2489,7 +2489,7 @@
         <v>7</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O22">
         <v>6</v>
@@ -2566,7 +2566,7 @@
         <v>6</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O23">
         <v>6</v>
@@ -2643,7 +2643,7 @@
         <v>8</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O24">
         <v>6</v>
@@ -2720,7 +2720,7 @@
         <v>6</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O25">
         <v>6</v>
@@ -2797,7 +2797,7 @@
         <v>9</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
         <v>7</v>
@@ -2903,7 +2903,7 @@
         <v>5</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O28">
         <v>5</v>
@@ -2980,7 +2980,7 @@
         <v>5</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O29">
         <v>5</v>
@@ -3057,7 +3057,7 @@
         <v>6</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O30">
         <v>5</v>
@@ -3075,7 +3075,7 @@
         <v>5</v>
       </c>
       <c r="T30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U30">
         <v>5</v>
@@ -3134,7 +3134,7 @@
         <v>9</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O31">
         <v>8</v>
@@ -3152,7 +3152,7 @@
         <v>7</v>
       </c>
       <c r="T31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U31">
         <v>7</v>
@@ -3211,7 +3211,7 @@
         <v>9</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O32">
         <v>7</v>
@@ -3288,7 +3288,7 @@
         <v>8</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
         <v>7</v>
@@ -3365,7 +3365,7 @@
         <v>6</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O34">
         <v>7</v>
@@ -3383,7 +3383,7 @@
         <v>8</v>
       </c>
       <c r="T34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U34">
         <v>6</v>
@@ -3442,7 +3442,7 @@
         <v>9</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
         <v>10</v>
@@ -3519,7 +3519,7 @@
         <v>7</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O36">
         <v>6</v>
@@ -3596,7 +3596,7 @@
         <v>10</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O37">
         <v>9</v>
@@ -3673,7 +3673,7 @@
         <v>10</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O38">
         <v>8</v>
@@ -3750,7 +3750,7 @@
         <v>6</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O39">
         <v>6</v>
@@ -3827,7 +3827,7 @@
         <v>10</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O40">
         <v>7</v>
@@ -3904,7 +3904,7 @@
         <v>9</v>
       </c>
       <c r="N41">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O41">
         <v>8</v>
@@ -3981,7 +3981,7 @@
         <v>5</v>
       </c>
       <c r="N42">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O42">
         <v>6</v>
@@ -4058,7 +4058,7 @@
         <v>7</v>
       </c>
       <c r="N43">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O43">
         <v>7</v>
@@ -4076,7 +4076,7 @@
         <v>6</v>
       </c>
       <c r="T43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U43">
         <v>6</v>
@@ -4135,7 +4135,7 @@
         <v>5</v>
       </c>
       <c r="N44">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O44">
         <v>7</v>
@@ -4153,7 +4153,7 @@
         <v>8</v>
       </c>
       <c r="T44">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U44">
         <v>8</v>
@@ -4212,7 +4212,7 @@
         <v>9</v>
       </c>
       <c r="N45">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O45">
         <v>7</v>
@@ -4289,7 +4289,7 @@
         <v>6</v>
       </c>
       <c r="N46">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O46">
         <v>7</v>
@@ -4366,7 +4366,7 @@
         <v>10</v>
       </c>
       <c r="N47">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O47">
         <v>7</v>
@@ -4443,7 +4443,7 @@
         <v>6</v>
       </c>
       <c r="N48">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O48">
         <v>6</v>
@@ -4713,7 +4713,7 @@
         <v>4.55</v>
       </c>
       <c r="H7">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
